--- a/research/traditional_assets/database/data/norway/norway_building_materials.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_building_materials.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0856626422568786</v>
+        <v>0.08550928444391348</v>
       </c>
       <c r="C2">
-        <v>202.6942228318287</v>
+        <v>200.8459350371665</v>
       </c>
       <c r="D2">
-        <v>199.9342228318287</v>
+        <v>200.4019350371665</v>
       </c>
       <c r="E2">
-        <v>-135.7</v>
+        <v>-133.384</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.316</v>
       </c>
       <c r="G2">
         <v>2.76</v>
@@ -1445,28 +1445,28 @@
         <v>21.07</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1164948</v>
       </c>
       <c r="N2">
-        <v>21.07</v>
+        <v>20.9535052</v>
       </c>
       <c r="O2">
-        <v>4.6354</v>
+        <v>4.609771144</v>
       </c>
       <c r="P2">
-        <v>16.4346</v>
+        <v>16.343734056</v>
       </c>
       <c r="Q2">
-        <v>24.8646</v>
+        <v>24.773734056</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0856626422568786</v>
+        <v>0.08597671155950856</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9278686272403823</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>180.8664421072872</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08550928444391348</v>
+        <v>0.08535592663094833</v>
       </c>
       <c r="C3">
-        <v>200.8459350371665</v>
+        <v>198.9998406403469</v>
       </c>
       <c r="D3">
-        <v>200.4019350371665</v>
+        <v>200.871840640347</v>
       </c>
       <c r="E3">
-        <v>-133.384</v>
+        <v>-131.068</v>
       </c>
       <c r="F3">
-        <v>2.316</v>
+        <v>4.632</v>
       </c>
       <c r="G3">
         <v>2.76</v>
@@ -1527,28 +1527,28 @@
         <v>21.07</v>
       </c>
       <c r="M3">
-        <v>0.1164948</v>
+        <v>0.2329896</v>
       </c>
       <c r="N3">
-        <v>20.9535052</v>
+        <v>20.8370104</v>
       </c>
       <c r="O3">
-        <v>4.609771144</v>
+        <v>4.584142288</v>
       </c>
       <c r="P3">
-        <v>16.343734056</v>
+        <v>16.252868112</v>
       </c>
       <c r="Q3">
-        <v>24.773734056</v>
+        <v>24.682868112</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08597671155950856</v>
+        <v>0.08629719043974321</v>
       </c>
       <c r="T3">
-        <v>0.9278686272403823</v>
+        <v>0.9352699870610439</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>180.8664421072872</v>
+        <v>90.43322105364361</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08535592663094833</v>
+        <v>0.08520256881798322</v>
       </c>
       <c r="C4">
-        <v>198.9998406403469</v>
+        <v>197.1559551069747</v>
       </c>
       <c r="D4">
-        <v>200.871840640347</v>
+        <v>201.3439551069748</v>
       </c>
       <c r="E4">
-        <v>-131.068</v>
+        <v>-128.752</v>
       </c>
       <c r="F4">
-        <v>4.632</v>
+        <v>6.948</v>
       </c>
       <c r="G4">
         <v>2.76</v>
@@ -1609,28 +1609,28 @@
         <v>21.07</v>
       </c>
       <c r="M4">
-        <v>0.2329896</v>
+        <v>0.3494844</v>
       </c>
       <c r="N4">
-        <v>20.8370104</v>
+        <v>20.7205156</v>
       </c>
       <c r="O4">
-        <v>4.584142288</v>
+        <v>4.558513432</v>
       </c>
       <c r="P4">
-        <v>16.252868112</v>
+        <v>16.162002168</v>
       </c>
       <c r="Q4">
-        <v>24.682868112</v>
+        <v>24.592002168</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08629719043974321</v>
+        <v>0.08662427713194146</v>
       </c>
       <c r="T4">
-        <v>0.9352699870610439</v>
+        <v>0.9428239522388325</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>90.43322105364361</v>
+        <v>60.2888140357624</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08520256881798322</v>
+        <v>0.08504921100501807</v>
       </c>
       <c r="C5">
-        <v>197.1559551069747</v>
+        <v>195.3142940483947</v>
       </c>
       <c r="D5">
-        <v>201.3439551069748</v>
+        <v>201.8182940483947</v>
       </c>
       <c r="E5">
-        <v>-128.752</v>
+        <v>-126.436</v>
       </c>
       <c r="F5">
-        <v>6.948</v>
+        <v>9.263999999999999</v>
       </c>
       <c r="G5">
         <v>2.76</v>
@@ -1691,28 +1691,28 @@
         <v>21.07</v>
       </c>
       <c r="M5">
-        <v>0.3494844</v>
+        <v>0.4659791999999999</v>
       </c>
       <c r="N5">
-        <v>20.7205156</v>
+        <v>20.6040208</v>
       </c>
       <c r="O5">
-        <v>4.558513432</v>
+        <v>4.532884576</v>
       </c>
       <c r="P5">
-        <v>16.162002168</v>
+        <v>16.071136224</v>
       </c>
       <c r="Q5">
-        <v>24.592002168</v>
+        <v>24.501136224</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08662427713194146</v>
+        <v>0.08695817813022716</v>
       </c>
       <c r="T5">
-        <v>0.9428239522388325</v>
+        <v>0.9505352916911584</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.2888140357624</v>
+        <v>45.2166105268218</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08504921100501807</v>
+        <v>0.08489585319205294</v>
       </c>
       <c r="C6">
-        <v>195.3142940483947</v>
+        <v>193.4748732234112</v>
       </c>
       <c r="D6">
-        <v>201.8182940483947</v>
+        <v>202.2948732234113</v>
       </c>
       <c r="E6">
-        <v>-126.436</v>
+        <v>-124.12</v>
       </c>
       <c r="F6">
-        <v>9.263999999999999</v>
+        <v>11.58</v>
       </c>
       <c r="G6">
         <v>2.76</v>
@@ -1773,28 +1773,28 @@
         <v>21.07</v>
       </c>
       <c r="M6">
-        <v>0.4659791999999999</v>
+        <v>0.5824739999999999</v>
       </c>
       <c r="N6">
-        <v>20.6040208</v>
+        <v>20.487526</v>
       </c>
       <c r="O6">
-        <v>4.532884576</v>
+        <v>4.50725572</v>
       </c>
       <c r="P6">
-        <v>16.071136224</v>
+        <v>15.98027028</v>
       </c>
       <c r="Q6">
-        <v>24.501136224</v>
+        <v>24.41027028</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08695817813022716</v>
+        <v>0.08729910862321362</v>
       </c>
       <c r="T6">
-        <v>0.9505352916911584</v>
+        <v>0.9584089751319543</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.2166105268218</v>
+        <v>36.17328842145744</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08489585319205294</v>
+        <v>0.0847424953790878</v>
       </c>
       <c r="C7">
-        <v>193.4748732234112</v>
+        <v>191.6377085400347</v>
       </c>
       <c r="D7">
-        <v>202.2948732234113</v>
+        <v>202.7737085400347</v>
       </c>
       <c r="E7">
-        <v>-124.12</v>
+        <v>-121.804</v>
       </c>
       <c r="F7">
-        <v>11.58</v>
+        <v>13.896</v>
       </c>
       <c r="G7">
         <v>2.76</v>
@@ -1855,28 +1855,28 @@
         <v>21.07</v>
       </c>
       <c r="M7">
-        <v>0.5824739999999999</v>
+        <v>0.6989688000000001</v>
       </c>
       <c r="N7">
-        <v>20.487526</v>
+        <v>20.3710312</v>
       </c>
       <c r="O7">
-        <v>4.50725572</v>
+        <v>4.481626864</v>
       </c>
       <c r="P7">
-        <v>15.98027028</v>
+        <v>15.889404336</v>
       </c>
       <c r="Q7">
-        <v>24.41027028</v>
+        <v>24.319404336</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08729910862321362</v>
+        <v>0.08764729295647639</v>
       </c>
       <c r="T7">
-        <v>0.9584089751319543</v>
+        <v>0.9664501837523415</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.17328842145744</v>
+        <v>30.1444070178812</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0847424953790878</v>
+        <v>0.08458913756612266</v>
       </c>
       <c r="C8">
-        <v>191.6377085400347</v>
+        <v>189.8028160572506</v>
       </c>
       <c r="D8">
-        <v>202.7737085400347</v>
+        <v>203.2548160572506</v>
       </c>
       <c r="E8">
-        <v>-121.804</v>
+        <v>-119.488</v>
       </c>
       <c r="F8">
-        <v>13.896</v>
+        <v>16.212</v>
       </c>
       <c r="G8">
         <v>2.76</v>
@@ -1937,28 +1937,28 @@
         <v>21.07</v>
       </c>
       <c r="M8">
-        <v>0.6989687999999999</v>
+        <v>0.8154635999999997</v>
       </c>
       <c r="N8">
-        <v>20.3710312</v>
+        <v>20.2545364</v>
       </c>
       <c r="O8">
-        <v>4.481626864</v>
+        <v>4.455998008</v>
       </c>
       <c r="P8">
-        <v>15.889404336</v>
+        <v>15.798538392</v>
       </c>
       <c r="Q8">
-        <v>24.319404336</v>
+        <v>24.228538392</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08764729295647639</v>
+        <v>0.08800296512486308</v>
       </c>
       <c r="T8">
-        <v>0.9664501837523415</v>
+        <v>0.9746643215903714</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.1444070178812</v>
+        <v>25.83806315818389</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08458913756612267</v>
+        <v>0.08443577975315752</v>
       </c>
       <c r="C9">
-        <v>189.8028160572505</v>
+        <v>187.9702119868152</v>
       </c>
       <c r="D9">
-        <v>203.2548160572505</v>
+        <v>203.7382119868152</v>
       </c>
       <c r="E9">
-        <v>-119.488</v>
+        <v>-117.172</v>
       </c>
       <c r="F9">
-        <v>16.212</v>
+        <v>18.528</v>
       </c>
       <c r="G9">
         <v>2.76</v>
@@ -2019,28 +2019,28 @@
         <v>21.07</v>
       </c>
       <c r="M9">
-        <v>0.8154636</v>
+        <v>0.9319583999999999</v>
       </c>
       <c r="N9">
-        <v>20.2545364</v>
+        <v>20.1380416</v>
       </c>
       <c r="O9">
-        <v>4.455998008</v>
+        <v>4.430369152</v>
       </c>
       <c r="P9">
-        <v>15.798538392</v>
+        <v>15.707672448</v>
       </c>
       <c r="Q9">
-        <v>24.228538392</v>
+        <v>24.137672448</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08800296512486308</v>
+        <v>0.08836636929691036</v>
       </c>
       <c r="T9">
-        <v>0.9746643215903716</v>
+        <v>0.9830570276422718</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.83806315818389</v>
+        <v>22.60830526341091</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08443577975315752</v>
+        <v>0.08428242194019242</v>
       </c>
       <c r="C10">
-        <v>187.9702119868152</v>
+        <v>186.1399126950765</v>
       </c>
       <c r="D10">
-        <v>203.7382119868152</v>
+        <v>204.2239126950765</v>
       </c>
       <c r="E10">
-        <v>-117.172</v>
+        <v>-114.856</v>
       </c>
       <c r="F10">
-        <v>18.528</v>
+        <v>20.844</v>
       </c>
       <c r="G10">
         <v>2.76</v>
@@ -2101,28 +2101,28 @@
         <v>21.07</v>
       </c>
       <c r="M10">
-        <v>0.9319583999999999</v>
+        <v>1.0484532</v>
       </c>
       <c r="N10">
-        <v>20.1380416</v>
+        <v>20.0215468</v>
       </c>
       <c r="O10">
-        <v>4.430369152</v>
+        <v>4.404740296</v>
       </c>
       <c r="P10">
-        <v>15.707672448</v>
+        <v>15.616806504</v>
       </c>
       <c r="Q10">
-        <v>24.137672448</v>
+        <v>24.046806504</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08836636929691036</v>
+        <v>0.08873776037383782</v>
       </c>
       <c r="T10">
-        <v>0.9830570276422718</v>
+        <v>0.9916341887722359</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.60830526341091</v>
+        <v>20.09627134525414</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08428242194019242</v>
+        <v>0.08412906412722727</v>
       </c>
       <c r="C11">
-        <v>186.1399126950765</v>
+        <v>184.3119347048218</v>
       </c>
       <c r="D11">
-        <v>204.2239126950765</v>
+        <v>204.7119347048218</v>
       </c>
       <c r="E11">
-        <v>-114.856</v>
+        <v>-112.54</v>
       </c>
       <c r="F11">
-        <v>20.844</v>
+        <v>23.16</v>
       </c>
       <c r="G11">
         <v>2.76</v>
@@ -2183,28 +2183,28 @@
         <v>21.07</v>
       </c>
       <c r="M11">
-        <v>1.0484532</v>
+        <v>1.164948</v>
       </c>
       <c r="N11">
-        <v>20.0215468</v>
+        <v>19.905052</v>
       </c>
       <c r="O11">
-        <v>4.404740296</v>
+        <v>4.37911144</v>
       </c>
       <c r="P11">
-        <v>15.616806504</v>
+        <v>15.52594056</v>
       </c>
       <c r="Q11">
-        <v>24.046806504</v>
+        <v>23.95594056</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08873776037383782</v>
+        <v>0.08911740458580808</v>
       </c>
       <c r="T11">
-        <v>0.9916341887722359</v>
+        <v>1.000401953482866</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.09627134525414</v>
+        <v>18.08664421072872</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08412906412722727</v>
+        <v>0.08397570631426214</v>
       </c>
       <c r="C12">
-        <v>184.3119347048218</v>
+        <v>182.4862946971502</v>
       </c>
       <c r="D12">
-        <v>204.7119347048218</v>
+        <v>205.2022946971502</v>
       </c>
       <c r="E12">
-        <v>-112.54</v>
+        <v>-110.224</v>
       </c>
       <c r="F12">
-        <v>23.16</v>
+        <v>25.476</v>
       </c>
       <c r="G12">
         <v>2.76</v>
@@ -2265,28 +2265,28 @@
         <v>21.07</v>
       </c>
       <c r="M12">
-        <v>1.164948</v>
+        <v>1.2814428</v>
       </c>
       <c r="N12">
-        <v>19.905052</v>
+        <v>19.7885572</v>
       </c>
       <c r="O12">
-        <v>4.37911144</v>
+        <v>4.353482584</v>
       </c>
       <c r="P12">
-        <v>15.52594056</v>
+        <v>15.435074616</v>
       </c>
       <c r="Q12">
-        <v>23.95594056</v>
+        <v>23.865074616</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08911740458580808</v>
+        <v>0.08950558012838443</v>
       </c>
       <c r="T12">
-        <v>1.000401953482866</v>
+        <v>1.009366746613959</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.08664421072872</v>
+        <v>16.4424038279352</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08397570631426214</v>
+        <v>0.08382234850129701</v>
       </c>
       <c r="C13">
-        <v>182.4862946971502</v>
+        <v>180.6630095133743</v>
       </c>
       <c r="D13">
-        <v>205.2022946971502</v>
+        <v>205.6950095133743</v>
       </c>
       <c r="E13">
-        <v>-110.224</v>
+        <v>-107.908</v>
       </c>
       <c r="F13">
-        <v>25.476</v>
+        <v>27.792</v>
       </c>
       <c r="G13">
         <v>2.76</v>
@@ -2347,28 +2347,28 @@
         <v>21.07</v>
       </c>
       <c r="M13">
-        <v>1.2814428</v>
+        <v>1.3979376</v>
       </c>
       <c r="N13">
-        <v>19.7885572</v>
+        <v>19.6720624</v>
       </c>
       <c r="O13">
-        <v>4.353482584</v>
+        <v>4.327853728</v>
       </c>
       <c r="P13">
-        <v>15.435074616</v>
+        <v>15.344208672</v>
       </c>
       <c r="Q13">
-        <v>23.865074616</v>
+        <v>23.774208672</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08950558012838443</v>
+        <v>0.08990257784238297</v>
       </c>
       <c r="T13">
-        <v>1.009366746613959</v>
+        <v>1.018535285043487</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.4424038279352</v>
+        <v>15.0722035089406</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08382234850129701</v>
+        <v>0.08366899068833186</v>
       </c>
       <c r="C14">
-        <v>180.6630095133743</v>
+        <v>178.8420961569479</v>
       </c>
       <c r="D14">
-        <v>205.6950095133743</v>
+        <v>206.1900961569479</v>
       </c>
       <c r="E14">
-        <v>-107.908</v>
+        <v>-105.592</v>
       </c>
       <c r="F14">
-        <v>27.792</v>
+        <v>30.108</v>
       </c>
       <c r="G14">
         <v>2.76</v>
@@ -2429,28 +2429,28 @@
         <v>21.07</v>
       </c>
       <c r="M14">
-        <v>1.3979376</v>
+        <v>1.5144324</v>
       </c>
       <c r="N14">
-        <v>19.6720624</v>
+        <v>19.5555676</v>
       </c>
       <c r="O14">
-        <v>4.327853728</v>
+        <v>4.302224872</v>
       </c>
       <c r="P14">
-        <v>15.344208672</v>
+        <v>15.253342728</v>
       </c>
       <c r="Q14">
-        <v>23.774208672</v>
+        <v>23.683342728</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08990257784238297</v>
+        <v>0.09030870194061134</v>
       </c>
       <c r="T14">
-        <v>1.018535285043487</v>
+        <v>1.027914594471394</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.0722035089406</v>
+        <v>13.91280323902209</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08366899068833186</v>
+        <v>0.08351563287536674</v>
       </c>
       <c r="C15">
-        <v>178.8420961569479</v>
+        <v>177.0235717954218</v>
       </c>
       <c r="D15">
-        <v>206.1900961569479</v>
+        <v>206.6875717954218</v>
       </c>
       <c r="E15">
-        <v>-105.592</v>
+        <v>-103.276</v>
       </c>
       <c r="F15">
-        <v>30.108</v>
+        <v>32.424</v>
       </c>
       <c r="G15">
         <v>2.76</v>
@@ -2511,28 +2511,28 @@
         <v>21.07</v>
       </c>
       <c r="M15">
-        <v>1.5144324</v>
+        <v>1.6309272</v>
       </c>
       <c r="N15">
-        <v>19.5555676</v>
+        <v>19.4390728</v>
       </c>
       <c r="O15">
-        <v>4.302224872</v>
+        <v>4.276596016</v>
       </c>
       <c r="P15">
-        <v>15.253342728</v>
+        <v>15.162476784</v>
       </c>
       <c r="Q15">
-        <v>23.683342728</v>
+        <v>23.592476784</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09030870194061134</v>
+        <v>0.09072427078531017</v>
       </c>
       <c r="T15">
-        <v>1.027914594471394</v>
+        <v>1.037512027374369</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.91280323902209</v>
+        <v>12.91903157909194</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08351563287536674</v>
+        <v>0.08353777506240161</v>
       </c>
       <c r="C16">
-        <v>177.0235717954218</v>
+        <v>174.6355967864978</v>
       </c>
       <c r="D16">
-        <v>206.6875717954218</v>
+        <v>206.6155967864978</v>
       </c>
       <c r="E16">
-        <v>-103.276</v>
+        <v>-100.96</v>
       </c>
       <c r="F16">
-        <v>32.424</v>
+        <v>34.74</v>
       </c>
       <c r="G16">
         <v>2.76</v>
@@ -2593,45 +2593,45 @@
         <v>21.07</v>
       </c>
       <c r="M16">
-        <v>1.6309272</v>
+        <v>1.799532</v>
       </c>
       <c r="N16">
-        <v>19.4390728</v>
+        <v>19.270468</v>
       </c>
       <c r="O16">
-        <v>4.276596016</v>
+        <v>4.23950296</v>
       </c>
       <c r="P16">
-        <v>15.162476784</v>
+        <v>15.03096504</v>
       </c>
       <c r="Q16">
-        <v>23.592476784</v>
+        <v>23.46096504</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09072427078531017</v>
+        <v>0.09114961772047248</v>
       </c>
       <c r="T16">
-        <v>1.037512027374369</v>
+        <v>1.047335282228002</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.22</v>
       </c>
       <c r="W16">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>12.91903157909194</v>
+        <v>11.70859979150135</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08353777506240161</v>
+        <v>0.08339611724943649</v>
       </c>
       <c r="C17">
-        <v>174.6355967864978</v>
+        <v>172.7809346599421</v>
       </c>
       <c r="D17">
-        <v>206.6155967864978</v>
+        <v>207.0769346599421</v>
       </c>
       <c r="E17">
-        <v>-100.96</v>
+        <v>-98.64399999999999</v>
       </c>
       <c r="F17">
-        <v>34.73999999999999</v>
+        <v>37.056</v>
       </c>
       <c r="G17">
         <v>2.76</v>
@@ -2675,28 +2675,28 @@
         <v>21.07</v>
       </c>
       <c r="M17">
-        <v>1.799532</v>
+        <v>1.9195008</v>
       </c>
       <c r="N17">
-        <v>19.270468</v>
+        <v>19.1504992</v>
       </c>
       <c r="O17">
-        <v>4.23950296</v>
+        <v>4.213109824</v>
       </c>
       <c r="P17">
-        <v>15.03096504</v>
+        <v>14.937389376</v>
       </c>
       <c r="Q17">
-        <v>23.46096504</v>
+        <v>23.367389376</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09114961772047248</v>
+        <v>0.09158509196361486</v>
       </c>
       <c r="T17">
-        <v>1.047335282228002</v>
+        <v>1.05739242410196</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.70859979150135</v>
+        <v>10.97681230453251</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08339611724943649</v>
+        <v>0.08325445943647135</v>
       </c>
       <c r="C18">
-        <v>172.7809346599421</v>
+        <v>170.9283373234577</v>
       </c>
       <c r="D18">
-        <v>207.0769346599421</v>
+        <v>207.5403373234577</v>
       </c>
       <c r="E18">
-        <v>-98.64399999999999</v>
+        <v>-96.32799999999999</v>
       </c>
       <c r="F18">
-        <v>37.056</v>
+        <v>39.372</v>
       </c>
       <c r="G18">
         <v>2.76</v>
@@ -2757,28 +2757,28 @@
         <v>21.07</v>
       </c>
       <c r="M18">
-        <v>1.9195008</v>
+        <v>2.0394696</v>
       </c>
       <c r="N18">
-        <v>19.1504992</v>
+        <v>19.0305304</v>
       </c>
       <c r="O18">
-        <v>4.213109824</v>
+        <v>4.186716688</v>
       </c>
       <c r="P18">
-        <v>14.937389376</v>
+        <v>14.843813712</v>
       </c>
       <c r="Q18">
-        <v>23.367389376</v>
+        <v>23.273813712</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09158509196361486</v>
+        <v>0.09203105956201367</v>
       </c>
       <c r="T18">
-        <v>1.05739242410196</v>
+        <v>1.067691906743965</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.97681230453251</v>
+        <v>10.33111746308942</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08325445943647135</v>
+        <v>0.08335148162350622</v>
       </c>
       <c r="C19">
-        <v>170.9283373234577</v>
+        <v>168.2947269268014</v>
       </c>
       <c r="D19">
-        <v>207.5403373234577</v>
+        <v>207.2227269268015</v>
       </c>
       <c r="E19">
-        <v>-96.32799999999999</v>
+        <v>-94.01199999999999</v>
       </c>
       <c r="F19">
-        <v>39.372</v>
+        <v>41.688</v>
       </c>
       <c r="G19">
         <v>2.76</v>
@@ -2839,45 +2839,45 @@
         <v>21.07</v>
       </c>
       <c r="M19">
-        <v>2.0394696</v>
+        <v>2.230308</v>
       </c>
       <c r="N19">
-        <v>19.0305304</v>
+        <v>18.839692</v>
       </c>
       <c r="O19">
-        <v>4.186716688</v>
+        <v>4.14473224</v>
       </c>
       <c r="P19">
-        <v>14.843813712</v>
+        <v>14.69495976</v>
       </c>
       <c r="Q19">
-        <v>23.273813712</v>
+        <v>23.12495976</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09203105956201367</v>
+        <v>0.09248790441891003</v>
       </c>
       <c r="T19">
-        <v>1.067691906743965</v>
+        <v>1.078242596279677</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.33111746308942</v>
+        <v>9.447125688469933</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08335148162350621</v>
+        <v>0.08322308381054108</v>
       </c>
       <c r="C20">
-        <v>168.2947269268015</v>
+        <v>166.399256545713</v>
       </c>
       <c r="D20">
-        <v>207.2227269268015</v>
+        <v>207.643256545713</v>
       </c>
       <c r="E20">
-        <v>-94.012</v>
+        <v>-91.696</v>
       </c>
       <c r="F20">
-        <v>41.688</v>
+        <v>44.004</v>
       </c>
       <c r="G20">
         <v>2.76</v>
@@ -2921,28 +2921,28 @@
         <v>21.07</v>
       </c>
       <c r="M20">
-        <v>2.230308</v>
+        <v>2.354214</v>
       </c>
       <c r="N20">
-        <v>18.839692</v>
+        <v>18.715786</v>
       </c>
       <c r="O20">
-        <v>4.14473224</v>
+        <v>4.11747292</v>
       </c>
       <c r="P20">
-        <v>14.69495976</v>
+        <v>14.59831308</v>
       </c>
       <c r="Q20">
-        <v>23.12495976</v>
+        <v>23.02831308</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09248790441891</v>
+        <v>0.09295602939572972</v>
       </c>
       <c r="T20">
-        <v>1.078242596279677</v>
+        <v>1.089053796668123</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.447125688469935</v>
+        <v>8.949908546971518</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08322308381054108</v>
+        <v>0.08309468599757595</v>
       </c>
       <c r="C21">
-        <v>166.399256545713</v>
+        <v>164.5054964478098</v>
       </c>
       <c r="D21">
-        <v>207.643256545713</v>
+        <v>208.0654964478098</v>
       </c>
       <c r="E21">
-        <v>-91.696</v>
+        <v>-89.38</v>
       </c>
       <c r="F21">
-        <v>44.004</v>
+        <v>46.32</v>
       </c>
       <c r="G21">
         <v>2.76</v>
@@ -3003,28 +3003,28 @@
         <v>21.07</v>
       </c>
       <c r="M21">
-        <v>2.354214</v>
+        <v>2.47812</v>
       </c>
       <c r="N21">
-        <v>18.715786</v>
+        <v>18.59188</v>
       </c>
       <c r="O21">
-        <v>4.11747292</v>
+        <v>4.0902136</v>
       </c>
       <c r="P21">
-        <v>14.59831308</v>
+        <v>14.5016664</v>
       </c>
       <c r="Q21">
-        <v>23.02831308</v>
+        <v>22.9316664</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09295602939572972</v>
+        <v>0.09343585749696993</v>
       </c>
       <c r="T21">
-        <v>1.089053796668123</v>
+        <v>1.10013527706628</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.949908546971518</v>
+        <v>8.50241311962294</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08309468599757595</v>
+        <v>0.08296628818461083</v>
       </c>
       <c r="C22">
-        <v>164.5054964478098</v>
+        <v>162.6134570878686</v>
       </c>
       <c r="D22">
-        <v>208.0654964478098</v>
+        <v>208.4894570878686</v>
       </c>
       <c r="E22">
-        <v>-89.38</v>
+        <v>-87.06399999999999</v>
       </c>
       <c r="F22">
-        <v>46.32</v>
+        <v>48.636</v>
       </c>
       <c r="G22">
         <v>2.76</v>
@@ -3085,28 +3085,28 @@
         <v>21.07</v>
       </c>
       <c r="M22">
-        <v>2.47812</v>
+        <v>2.602026</v>
       </c>
       <c r="N22">
-        <v>18.59188</v>
+        <v>18.467974</v>
       </c>
       <c r="O22">
-        <v>4.0902136</v>
+        <v>4.06295428</v>
       </c>
       <c r="P22">
-        <v>14.5016664</v>
+        <v>14.40501972</v>
       </c>
       <c r="Q22">
-        <v>22.9316664</v>
+        <v>22.83501972</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09343585749696993</v>
+        <v>0.09392783314507698</v>
       </c>
       <c r="T22">
-        <v>1.10013527706628</v>
+        <v>1.111497301271986</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.50241311962294</v>
+        <v>8.097536304402801</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08296628818461081</v>
+        <v>0.08283789037164567</v>
       </c>
       <c r="C23">
-        <v>162.6134570878687</v>
+        <v>160.7231490060518</v>
       </c>
       <c r="D23">
-        <v>208.4894570878687</v>
+        <v>208.9151490060518</v>
       </c>
       <c r="E23">
-        <v>-87.06399999999999</v>
+        <v>-84.74799999999999</v>
       </c>
       <c r="F23">
-        <v>48.636</v>
+        <v>50.952</v>
       </c>
       <c r="G23">
         <v>2.76</v>
@@ -3167,28 +3167,28 @@
         <v>21.07</v>
       </c>
       <c r="M23">
-        <v>2.602026</v>
+        <v>2.725932</v>
       </c>
       <c r="N23">
-        <v>18.467974</v>
+        <v>18.344068</v>
       </c>
       <c r="O23">
-        <v>4.06295428</v>
+        <v>4.03569496</v>
       </c>
       <c r="P23">
-        <v>14.40501972</v>
+        <v>14.30837304</v>
       </c>
       <c r="Q23">
-        <v>22.83501972</v>
+        <v>22.73837304</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09392783314507697</v>
+        <v>0.09443242355339189</v>
       </c>
       <c r="T23">
-        <v>1.111497301271986</v>
+        <v>1.123150659431683</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.097536304402801</v>
+        <v>7.729466472384491</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08283789037164567</v>
+        <v>0.08285301255868055</v>
       </c>
       <c r="C24">
-        <v>160.7231490060518</v>
+        <v>158.3569224044108</v>
       </c>
       <c r="D24">
-        <v>208.9151490060518</v>
+        <v>208.8649224044108</v>
       </c>
       <c r="E24">
-        <v>-84.74799999999999</v>
+        <v>-82.43199999999999</v>
       </c>
       <c r="F24">
-        <v>50.952</v>
+        <v>53.268</v>
       </c>
       <c r="G24">
         <v>2.76</v>
@@ -3249,45 +3249,45 @@
         <v>21.07</v>
       </c>
       <c r="M24">
-        <v>2.725932</v>
+        <v>2.8924524</v>
       </c>
       <c r="N24">
-        <v>18.344068</v>
+        <v>18.1775476</v>
       </c>
       <c r="O24">
-        <v>4.03569496</v>
+        <v>3.999060472</v>
       </c>
       <c r="P24">
-        <v>14.30837304</v>
+        <v>14.178487128</v>
       </c>
       <c r="Q24">
-        <v>22.73837304</v>
+        <v>22.608487128</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09443242355339189</v>
+        <v>0.09495012020607863</v>
       </c>
       <c r="T24">
-        <v>1.123150659431683</v>
+        <v>1.135106702218906</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.22</v>
       </c>
       <c r="W24">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.729466472384491</v>
+        <v>7.284475969250177</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08285301255868055</v>
+        <v>0.08273085474571541</v>
       </c>
       <c r="C25">
-        <v>158.3569224044108</v>
+        <v>156.44734727433</v>
       </c>
       <c r="D25">
-        <v>208.8649224044108</v>
+        <v>209.27134727433</v>
       </c>
       <c r="E25">
-        <v>-82.43199999999999</v>
+        <v>-80.11599999999999</v>
       </c>
       <c r="F25">
-        <v>53.268</v>
+        <v>55.584</v>
       </c>
       <c r="G25">
         <v>2.76</v>
@@ -3331,28 +3331,28 @@
         <v>21.07</v>
       </c>
       <c r="M25">
-        <v>2.8924524</v>
+        <v>3.0182112</v>
       </c>
       <c r="N25">
-        <v>18.1775476</v>
+        <v>18.0517888</v>
       </c>
       <c r="O25">
-        <v>3.999060472</v>
+        <v>3.971393536</v>
       </c>
       <c r="P25">
-        <v>14.178487128</v>
+        <v>14.080395264</v>
       </c>
       <c r="Q25">
-        <v>22.608487128</v>
+        <v>22.510395264</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09495012020607863</v>
+        <v>0.0954814404548887</v>
       </c>
       <c r="T25">
-        <v>1.135106702218906</v>
+        <v>1.147377377711055</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.284475969250177</v>
+        <v>6.980956137198086</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08273085474571541</v>
+        <v>0.08260869693275028</v>
       </c>
       <c r="C26">
-        <v>156.44734727433</v>
+        <v>154.5393569314066</v>
       </c>
       <c r="D26">
-        <v>209.27134727433</v>
+        <v>209.6793569314067</v>
       </c>
       <c r="E26">
-        <v>-80.11599999999999</v>
+        <v>-77.79999999999998</v>
       </c>
       <c r="F26">
-        <v>55.584</v>
+        <v>57.9</v>
       </c>
       <c r="G26">
         <v>2.76</v>
@@ -3413,28 +3413,28 @@
         <v>21.07</v>
       </c>
       <c r="M26">
-        <v>3.0182112</v>
+        <v>3.14397</v>
       </c>
       <c r="N26">
-        <v>18.0517888</v>
+        <v>17.92603</v>
       </c>
       <c r="O26">
-        <v>3.971393536</v>
+        <v>3.9437266</v>
       </c>
       <c r="P26">
-        <v>14.080395264</v>
+        <v>13.9823034</v>
       </c>
       <c r="Q26">
-        <v>22.510395264</v>
+        <v>22.4123034</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0954814404548887</v>
+        <v>0.09602692924366704</v>
       </c>
       <c r="T26">
-        <v>1.147377377711055</v>
+        <v>1.159975271216329</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.980956137198087</v>
+        <v>6.701717891710163</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08260869693275028</v>
+        <v>0.08248653911978515</v>
       </c>
       <c r="C27">
-        <v>154.5393569314066</v>
+        <v>152.6329606631751</v>
       </c>
       <c r="D27">
-        <v>209.6793569314067</v>
+        <v>210.0889606631751</v>
       </c>
       <c r="E27">
-        <v>-77.79999999999998</v>
+        <v>-75.48399999999998</v>
       </c>
       <c r="F27">
-        <v>57.9</v>
+        <v>60.216</v>
       </c>
       <c r="G27">
         <v>2.76</v>
@@ -3495,28 +3495,28 @@
         <v>21.07</v>
       </c>
       <c r="M27">
-        <v>3.14397</v>
+        <v>3.2697288</v>
       </c>
       <c r="N27">
-        <v>17.92603</v>
+        <v>17.8002712</v>
       </c>
       <c r="O27">
-        <v>3.9437266</v>
+        <v>3.916059664</v>
       </c>
       <c r="P27">
-        <v>13.9823034</v>
+        <v>13.884211536</v>
       </c>
       <c r="Q27">
-        <v>22.4123034</v>
+        <v>22.314211536</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09602692924366704</v>
+        <v>0.09658716097268263</v>
       </c>
       <c r="T27">
-        <v>1.159975271216329</v>
+        <v>1.172913648329853</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.701717891710163</v>
+        <v>6.443959511259772</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08248653911978515</v>
+        <v>0.08236438130682001</v>
       </c>
       <c r="C28">
-        <v>152.6329606631751</v>
+        <v>150.7281678298835</v>
       </c>
       <c r="D28">
-        <v>210.0889606631751</v>
+        <v>210.5001678298836</v>
       </c>
       <c r="E28">
-        <v>-75.48399999999998</v>
+        <v>-73.16799999999998</v>
       </c>
       <c r="F28">
-        <v>60.216</v>
+        <v>62.532</v>
       </c>
       <c r="G28">
         <v>2.76</v>
@@ -3577,28 +3577,28 @@
         <v>21.07</v>
       </c>
       <c r="M28">
-        <v>3.2697288</v>
+        <v>3.3954876</v>
       </c>
       <c r="N28">
-        <v>17.8002712</v>
+        <v>17.6745124</v>
       </c>
       <c r="O28">
-        <v>3.916059664</v>
+        <v>3.888392728</v>
       </c>
       <c r="P28">
-        <v>13.884211536</v>
+        <v>13.786119672</v>
       </c>
       <c r="Q28">
-        <v>22.314211536</v>
+        <v>22.216119672</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09658716097268263</v>
+        <v>0.09716274151619179</v>
       </c>
       <c r="T28">
-        <v>1.172913648329853</v>
+        <v>1.186206501528679</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.443959511259772</v>
+        <v>6.205294344176076</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08236438130682001</v>
+        <v>0.0824606234938549</v>
       </c>
       <c r="C29">
-        <v>150.7281678298835</v>
+        <v>148.0880634270807</v>
       </c>
       <c r="D29">
-        <v>210.5001678298836</v>
+        <v>210.1760634270807</v>
       </c>
       <c r="E29">
-        <v>-73.16799999999998</v>
+        <v>-70.85199999999999</v>
       </c>
       <c r="F29">
-        <v>62.532</v>
+        <v>64.848</v>
       </c>
       <c r="G29">
         <v>2.76</v>
@@ -3659,45 +3659,45 @@
         <v>21.07</v>
       </c>
       <c r="M29">
-        <v>3.3954876</v>
+        <v>3.5860944</v>
       </c>
       <c r="N29">
-        <v>17.6745124</v>
+        <v>17.4839056</v>
       </c>
       <c r="O29">
-        <v>3.888392728</v>
+        <v>3.846459232</v>
       </c>
       <c r="P29">
-        <v>13.786119672</v>
+        <v>13.637446368</v>
       </c>
       <c r="Q29">
-        <v>22.216119672</v>
+        <v>22.067446368</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09716274151619179</v>
+        <v>0.09775431040813179</v>
       </c>
       <c r="T29">
-        <v>1.186206501528679</v>
+        <v>1.199868600649695</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.22</v>
       </c>
       <c r="W29">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.205294344176076</v>
+        <v>5.875472770599681</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0824606234938549</v>
+        <v>0.08234626568088976</v>
       </c>
       <c r="C30">
-        <v>148.0880634270807</v>
+        <v>146.1572856789848</v>
       </c>
       <c r="D30">
-        <v>210.1760634270807</v>
+        <v>210.5612856789848</v>
       </c>
       <c r="E30">
-        <v>-70.85199999999999</v>
+        <v>-68.53599999999999</v>
       </c>
       <c r="F30">
-        <v>64.848</v>
+        <v>67.164</v>
       </c>
       <c r="G30">
         <v>2.76</v>
@@ -3741,28 +3741,28 @@
         <v>21.07</v>
       </c>
       <c r="M30">
-        <v>3.5860944</v>
+        <v>3.7141692</v>
       </c>
       <c r="N30">
-        <v>17.4839056</v>
+        <v>17.3558308</v>
       </c>
       <c r="O30">
-        <v>3.846459232</v>
+        <v>3.818282776</v>
       </c>
       <c r="P30">
-        <v>13.637446368</v>
+        <v>13.537548024</v>
       </c>
       <c r="Q30">
-        <v>22.067446368</v>
+        <v>21.967548024</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09775431040813179</v>
+        <v>0.09836254321252078</v>
       </c>
       <c r="T30">
-        <v>1.199868600649695</v>
+        <v>1.213915547633274</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.875472770599681</v>
+        <v>5.672870261268657</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08234626568088975</v>
+        <v>0.08223190786792461</v>
       </c>
       <c r="C31">
-        <v>146.1572856789849</v>
+        <v>144.2279226369127</v>
       </c>
       <c r="D31">
-        <v>210.5612856789849</v>
+        <v>210.9479226369127</v>
       </c>
       <c r="E31">
-        <v>-68.536</v>
+        <v>-66.22</v>
       </c>
       <c r="F31">
-        <v>67.16399999999999</v>
+        <v>69.47999999999999</v>
       </c>
       <c r="G31">
         <v>2.76</v>
@@ -3823,28 +3823,28 @@
         <v>21.07</v>
       </c>
       <c r="M31">
-        <v>3.714169199999999</v>
+        <v>3.842244</v>
       </c>
       <c r="N31">
-        <v>17.3558308</v>
+        <v>17.227756</v>
       </c>
       <c r="O31">
-        <v>3.818282776</v>
+        <v>3.79010632</v>
       </c>
       <c r="P31">
-        <v>13.537548024</v>
+        <v>13.43764968</v>
       </c>
       <c r="Q31">
-        <v>21.967548024</v>
+        <v>21.86764968</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09836254321252078</v>
+        <v>0.09898815409703517</v>
       </c>
       <c r="T31">
-        <v>1.213915547633274</v>
+        <v>1.228363835959242</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.672870261268658</v>
+        <v>5.483774585893036</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08223190786792461</v>
+        <v>0.08211755005495948</v>
       </c>
       <c r="C32">
-        <v>144.2279226369127</v>
+        <v>142.2999821083372</v>
       </c>
       <c r="D32">
-        <v>210.9479226369127</v>
+        <v>211.3359821083372</v>
       </c>
       <c r="E32">
-        <v>-66.22</v>
+        <v>-63.904</v>
       </c>
       <c r="F32">
-        <v>69.47999999999999</v>
+        <v>71.79599999999999</v>
       </c>
       <c r="G32">
         <v>2.76</v>
@@ -3905,28 +3905,28 @@
         <v>21.07</v>
       </c>
       <c r="M32">
-        <v>3.842244</v>
+        <v>3.9703188</v>
       </c>
       <c r="N32">
-        <v>17.227756</v>
+        <v>17.0996812</v>
       </c>
       <c r="O32">
-        <v>3.79010632</v>
+        <v>3.761929864</v>
       </c>
       <c r="P32">
-        <v>13.43764968</v>
+        <v>13.337751336</v>
       </c>
       <c r="Q32">
-        <v>21.86764968</v>
+        <v>21.767751336</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09898815409703517</v>
+        <v>0.09963189863037607</v>
       </c>
       <c r="T32">
-        <v>1.228363835959242</v>
+        <v>1.243230915251179</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.483774585893036</v>
+        <v>5.306878631509389</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08211755005495948</v>
+        <v>0.08200319224199434</v>
       </c>
       <c r="C33">
-        <v>142.2999821083372</v>
+        <v>140.3734719582879</v>
       </c>
       <c r="D33">
-        <v>211.3359821083372</v>
+        <v>211.7254719582879</v>
       </c>
       <c r="E33">
-        <v>-63.904</v>
+        <v>-61.58799999999999</v>
       </c>
       <c r="F33">
-        <v>71.79599999999999</v>
+        <v>74.11199999999999</v>
       </c>
       <c r="G33">
         <v>2.76</v>
@@ -3987,28 +3987,28 @@
         <v>21.07</v>
       </c>
       <c r="M33">
-        <v>3.9703188</v>
+        <v>4.0983936</v>
       </c>
       <c r="N33">
-        <v>17.0996812</v>
+        <v>16.9716064</v>
       </c>
       <c r="O33">
-        <v>3.761929864</v>
+        <v>3.733753408</v>
       </c>
       <c r="P33">
-        <v>13.337751336</v>
+        <v>13.237852992</v>
       </c>
       <c r="Q33">
-        <v>21.767751336</v>
+        <v>21.667852992</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09963189863037607</v>
+        <v>0.1002945768264623</v>
       </c>
       <c r="T33">
-        <v>1.243230915251179</v>
+        <v>1.258535261581115</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.306878631509389</v>
+        <v>5.14103867427472</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08200319224199434</v>
+        <v>0.08188883442902922</v>
       </c>
       <c r="C34">
-        <v>140.3734719582879</v>
+        <v>138.4484001098816</v>
       </c>
       <c r="D34">
-        <v>211.7254719582879</v>
+        <v>212.1164001098816</v>
       </c>
       <c r="E34">
-        <v>-61.58799999999999</v>
+        <v>-59.27199999999999</v>
       </c>
       <c r="F34">
-        <v>74.11199999999999</v>
+        <v>76.428</v>
       </c>
       <c r="G34">
         <v>2.76</v>
@@ -4069,28 +4069,28 @@
         <v>21.07</v>
       </c>
       <c r="M34">
-        <v>4.0983936</v>
+        <v>4.2264684</v>
       </c>
       <c r="N34">
-        <v>16.9716064</v>
+        <v>16.8435316</v>
       </c>
       <c r="O34">
-        <v>3.733753408</v>
+        <v>3.705576952</v>
       </c>
       <c r="P34">
-        <v>13.237852992</v>
+        <v>13.137954648</v>
       </c>
       <c r="Q34">
-        <v>21.667852992</v>
+        <v>21.567954648</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1002945768264623</v>
+        <v>0.1009770364612376</v>
       </c>
       <c r="T34">
-        <v>1.258535261581115</v>
+        <v>1.274296454070153</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.14103867427472</v>
+        <v>4.985249623539123</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08188883442902922</v>
+        <v>0.08177447661606407</v>
       </c>
       <c r="C35">
-        <v>138.4484001098816</v>
+        <v>136.5247745448605</v>
       </c>
       <c r="D35">
-        <v>212.1164001098816</v>
+        <v>212.5087745448605</v>
       </c>
       <c r="E35">
-        <v>-59.27199999999999</v>
+        <v>-56.95599999999999</v>
       </c>
       <c r="F35">
-        <v>76.428</v>
+        <v>78.744</v>
       </c>
       <c r="G35">
         <v>2.76</v>
@@ -4151,28 +4151,28 @@
         <v>21.07</v>
       </c>
       <c r="M35">
-        <v>4.2264684</v>
+        <v>4.3545432</v>
       </c>
       <c r="N35">
-        <v>16.8435316</v>
+        <v>16.7154568</v>
       </c>
       <c r="O35">
-        <v>3.705576952</v>
+        <v>3.677400496</v>
       </c>
       <c r="P35">
-        <v>13.137954648</v>
+        <v>13.038056304</v>
       </c>
       <c r="Q35">
-        <v>21.567954648</v>
+        <v>21.468056304</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1009770364612376</v>
+        <v>0.1016801766910062</v>
       </c>
       <c r="T35">
-        <v>1.274296454070153</v>
+        <v>1.290535258452799</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.985249623539123</v>
+        <v>4.838624634611501</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08177447661606407</v>
+        <v>0.08166011880309895</v>
       </c>
       <c r="C36">
-        <v>136.5247745448605</v>
+        <v>134.6026033041347</v>
       </c>
       <c r="D36">
-        <v>212.5087745448605</v>
+        <v>212.9026033041347</v>
       </c>
       <c r="E36">
-        <v>-56.95599999999999</v>
+        <v>-54.63999999999999</v>
       </c>
       <c r="F36">
-        <v>78.744</v>
+        <v>81.06</v>
       </c>
       <c r="G36">
         <v>2.76</v>
@@ -4233,28 +4233,28 @@
         <v>21.07</v>
       </c>
       <c r="M36">
-        <v>4.3545432</v>
+        <v>4.482618</v>
       </c>
       <c r="N36">
-        <v>16.7154568</v>
+        <v>16.587382</v>
       </c>
       <c r="O36">
-        <v>3.677400496</v>
+        <v>3.64922404</v>
       </c>
       <c r="P36">
-        <v>13.038056304</v>
+        <v>12.93815796</v>
       </c>
       <c r="Q36">
-        <v>21.468056304</v>
+        <v>21.36815796</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1016801766910062</v>
+        <v>0.1024049520047676</v>
       </c>
       <c r="T36">
-        <v>1.290535258452799</v>
+        <v>1.30727371835491</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.838624634611501</v>
+        <v>4.700378216479744</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08166011880309895</v>
+        <v>0.0815457609901338</v>
       </c>
       <c r="C37">
-        <v>134.6026033041347</v>
+        <v>132.6818944883321</v>
       </c>
       <c r="D37">
-        <v>212.9026033041347</v>
+        <v>213.2978944883321</v>
       </c>
       <c r="E37">
-        <v>-54.63999999999999</v>
+        <v>-52.32399999999998</v>
       </c>
       <c r="F37">
-        <v>81.06</v>
+        <v>83.376</v>
       </c>
       <c r="G37">
         <v>2.76</v>
@@ -4315,28 +4315,28 @@
         <v>21.07</v>
       </c>
       <c r="M37">
-        <v>4.482618</v>
+        <v>4.610692800000001</v>
       </c>
       <c r="N37">
-        <v>16.587382</v>
+        <v>16.4593072</v>
       </c>
       <c r="O37">
-        <v>3.64922404</v>
+        <v>3.621047583999999</v>
       </c>
       <c r="P37">
-        <v>12.93815796</v>
+        <v>12.838259616</v>
       </c>
       <c r="Q37">
-        <v>21.36815796</v>
+        <v>21.268259616</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1024049520047676</v>
+        <v>0.1031523765470841</v>
       </c>
       <c r="T37">
-        <v>1.30727371835491</v>
+        <v>1.324535255128963</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.700378216479744</v>
+        <v>4.569812154910862</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08154576099013382</v>
+        <v>0.08215290317716868</v>
       </c>
       <c r="C38">
-        <v>132.681894488332</v>
+        <v>128.283863165688</v>
       </c>
       <c r="D38">
-        <v>213.297894488332</v>
+        <v>211.215863165688</v>
       </c>
       <c r="E38">
-        <v>-52.324</v>
+        <v>-50.008</v>
       </c>
       <c r="F38">
-        <v>83.37599999999999</v>
+        <v>85.69199999999999</v>
       </c>
       <c r="G38">
         <v>2.76</v>
@@ -4397,45 +4397,45 @@
         <v>21.07</v>
       </c>
       <c r="M38">
-        <v>4.6106928</v>
+        <v>4.9529976</v>
       </c>
       <c r="N38">
-        <v>16.4593072</v>
+        <v>16.1170024</v>
       </c>
       <c r="O38">
-        <v>3.621047584</v>
+        <v>3.545740528</v>
       </c>
       <c r="P38">
-        <v>12.838259616</v>
+        <v>12.571261872</v>
       </c>
       <c r="Q38">
-        <v>21.268259616</v>
+        <v>21.001261872</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1031523765470841</v>
+        <v>0.1039235288526487</v>
       </c>
       <c r="T38">
-        <v>1.324535255128963</v>
+        <v>1.34234477719743</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.22</v>
       </c>
       <c r="W38">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.569812154910863</v>
+        <v>4.253989543625057</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08215290317716868</v>
+        <v>0.08205804536420355</v>
       </c>
       <c r="C39">
-        <v>128.283863165688</v>
+        <v>126.2904693917746</v>
       </c>
       <c r="D39">
-        <v>211.215863165688</v>
+        <v>211.5384693917746</v>
       </c>
       <c r="E39">
-        <v>-50.008</v>
+        <v>-47.69199999999999</v>
       </c>
       <c r="F39">
-        <v>85.69199999999999</v>
+        <v>88.008</v>
       </c>
       <c r="G39">
         <v>2.76</v>
@@ -4479,28 +4479,28 @@
         <v>21.07</v>
       </c>
       <c r="M39">
-        <v>4.9529976</v>
+        <v>5.0868624</v>
       </c>
       <c r="N39">
-        <v>16.1170024</v>
+        <v>15.9831376</v>
       </c>
       <c r="O39">
-        <v>3.545740528</v>
+        <v>3.516290272</v>
       </c>
       <c r="P39">
-        <v>12.571261872</v>
+        <v>12.466847328</v>
       </c>
       <c r="Q39">
-        <v>21.001261872</v>
+        <v>20.896847328</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1039235288526487</v>
+        <v>0.104719557039038</v>
       </c>
       <c r="T39">
-        <v>1.34234477719743</v>
+        <v>1.360728799977783</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.253989543625057</v>
+        <v>4.142042450371765</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08205804536420355</v>
+        <v>0.08196318755123842</v>
       </c>
       <c r="C40">
-        <v>126.2904693917746</v>
+        <v>124.2980626079491</v>
       </c>
       <c r="D40">
-        <v>211.5384693917746</v>
+        <v>211.8620626079491</v>
       </c>
       <c r="E40">
-        <v>-47.69199999999999</v>
+        <v>-45.37599999999999</v>
       </c>
       <c r="F40">
-        <v>88.008</v>
+        <v>90.324</v>
       </c>
       <c r="G40">
         <v>2.76</v>
@@ -4561,28 +4561,28 @@
         <v>21.07</v>
       </c>
       <c r="M40">
-        <v>5.0868624</v>
+        <v>5.220727200000001</v>
       </c>
       <c r="N40">
-        <v>15.9831376</v>
+        <v>15.8492728</v>
       </c>
       <c r="O40">
-        <v>3.516290272</v>
+        <v>3.486840016</v>
       </c>
       <c r="P40">
-        <v>12.466847328</v>
+        <v>12.362432784</v>
       </c>
       <c r="Q40">
-        <v>20.896847328</v>
+        <v>20.792432784</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.104719557039038</v>
+        <v>0.1055416845102269</v>
       </c>
       <c r="T40">
-        <v>1.360728799977783</v>
+        <v>1.379715577603393</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.142042450371765</v>
+        <v>4.035836233695566</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08196318755123842</v>
+        <v>0.08296032973827329</v>
       </c>
       <c r="C41">
-        <v>124.2980626079491</v>
+        <v>118.6291734163388</v>
       </c>
       <c r="D41">
-        <v>211.8620626079491</v>
+        <v>208.5091734163388</v>
       </c>
       <c r="E41">
-        <v>-45.37599999999999</v>
+        <v>-43.05999999999999</v>
       </c>
       <c r="F41">
-        <v>90.324</v>
+        <v>92.64</v>
       </c>
       <c r="G41">
         <v>2.76</v>
@@ -4643,45 +4643,45 @@
         <v>21.07</v>
       </c>
       <c r="M41">
-        <v>5.220727200000001</v>
+        <v>5.678832</v>
       </c>
       <c r="N41">
-        <v>15.8492728</v>
+        <v>15.391168</v>
       </c>
       <c r="O41">
-        <v>3.486840016</v>
+        <v>3.38605696</v>
       </c>
       <c r="P41">
-        <v>12.362432784</v>
+        <v>12.00511104</v>
       </c>
       <c r="Q41">
-        <v>20.792432784</v>
+        <v>20.43511104</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1055416845102269</v>
+        <v>0.1063912162304555</v>
       </c>
       <c r="T41">
-        <v>1.379715577603393</v>
+        <v>1.399335247816524</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.22</v>
       </c>
       <c r="W41">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.035836233695566</v>
+        <v>3.710269999182931</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08296032973827329</v>
+        <v>0.08289277192530814</v>
       </c>
       <c r="C42">
-        <v>118.6291734163388</v>
+        <v>116.5369813987217</v>
       </c>
       <c r="D42">
-        <v>208.5091734163388</v>
+        <v>208.7329813987218</v>
       </c>
       <c r="E42">
-        <v>-43.05999999999999</v>
+        <v>-40.74399999999999</v>
       </c>
       <c r="F42">
-        <v>92.64</v>
+        <v>94.956</v>
       </c>
       <c r="G42">
         <v>2.76</v>
@@ -4725,28 +4725,28 @@
         <v>21.07</v>
       </c>
       <c r="M42">
-        <v>5.678832</v>
+        <v>5.8208028</v>
       </c>
       <c r="N42">
-        <v>15.391168</v>
+        <v>15.2491972</v>
       </c>
       <c r="O42">
-        <v>3.38605696</v>
+        <v>3.354823384</v>
       </c>
       <c r="P42">
-        <v>12.00511104</v>
+        <v>11.894373816</v>
       </c>
       <c r="Q42">
-        <v>20.43511104</v>
+        <v>20.324373816</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1063912162304555</v>
+        <v>0.1072695456361155</v>
       </c>
       <c r="T42">
-        <v>1.399335247816524</v>
+        <v>1.419619991596201</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.710269999182931</v>
+        <v>3.619775608958957</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08289277192530814</v>
+        <v>0.082825214112343</v>
       </c>
       <c r="C43">
-        <v>116.5369813987217</v>
+        <v>114.4452703559717</v>
       </c>
       <c r="D43">
-        <v>208.7329813987218</v>
+        <v>208.9572703559718</v>
       </c>
       <c r="E43">
-        <v>-40.74399999999999</v>
+        <v>-38.42799999999998</v>
       </c>
       <c r="F43">
-        <v>94.956</v>
+        <v>97.27200000000001</v>
       </c>
       <c r="G43">
         <v>2.76</v>
@@ -4807,28 +4807,28 @@
         <v>21.07</v>
       </c>
       <c r="M43">
-        <v>5.8208028</v>
+        <v>5.9627736</v>
       </c>
       <c r="N43">
-        <v>15.2491972</v>
+        <v>15.1072264</v>
       </c>
       <c r="O43">
-        <v>3.354823384</v>
+        <v>3.323589808</v>
       </c>
       <c r="P43">
-        <v>11.894373816</v>
+        <v>11.783636592</v>
       </c>
       <c r="Q43">
-        <v>20.324373816</v>
+        <v>20.213636592</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1072695456361155</v>
+        <v>0.1081781622626604</v>
       </c>
       <c r="T43">
-        <v>1.419619991596201</v>
+        <v>1.440604209299316</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.619775608958957</v>
+        <v>3.533590475412315</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08282521411234302</v>
+        <v>0.08369677629937788</v>
       </c>
       <c r="C44">
-        <v>114.4452703559717</v>
+        <v>109.272218870157</v>
       </c>
       <c r="D44">
-        <v>208.9572703559717</v>
+        <v>206.100218870157</v>
       </c>
       <c r="E44">
-        <v>-38.428</v>
+        <v>-36.11199999999999</v>
       </c>
       <c r="F44">
-        <v>97.27199999999999</v>
+        <v>99.58799999999999</v>
       </c>
       <c r="G44">
         <v>2.76</v>
@@ -4889,45 +4889,45 @@
         <v>21.07</v>
       </c>
       <c r="M44">
-        <v>5.962773599999999</v>
+        <v>6.3835908</v>
       </c>
       <c r="N44">
-        <v>15.1072264</v>
+        <v>14.6864092</v>
       </c>
       <c r="O44">
-        <v>3.323589808</v>
+        <v>3.231010024</v>
       </c>
       <c r="P44">
-        <v>11.783636592</v>
+        <v>11.455399176</v>
       </c>
       <c r="Q44">
-        <v>20.213636592</v>
+        <v>19.885399176</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1081781622626604</v>
+        <v>0.1091186601743472</v>
       </c>
       <c r="T44">
-        <v>1.440604209299316</v>
+        <v>1.462324715342891</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.22</v>
       </c>
       <c r="W44">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.533590475412316</v>
+        <v>3.300650160721454</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08369677629937788</v>
+        <v>0.08365105848641277</v>
       </c>
       <c r="C45">
-        <v>109.272218870157</v>
+        <v>107.1041425468872</v>
       </c>
       <c r="D45">
-        <v>206.100218870157</v>
+        <v>206.2481425468872</v>
       </c>
       <c r="E45">
-        <v>-36.11199999999999</v>
+        <v>-33.79599999999999</v>
       </c>
       <c r="F45">
-        <v>99.58799999999999</v>
+        <v>101.904</v>
       </c>
       <c r="G45">
         <v>2.76</v>
@@ -4971,28 +4971,28 @@
         <v>21.07</v>
       </c>
       <c r="M45">
-        <v>6.3835908</v>
+        <v>6.5320464</v>
       </c>
       <c r="N45">
-        <v>14.6864092</v>
+        <v>14.5379536</v>
       </c>
       <c r="O45">
-        <v>3.231010024</v>
+        <v>3.198349792</v>
       </c>
       <c r="P45">
-        <v>11.455399176</v>
+        <v>11.339603808</v>
       </c>
       <c r="Q45">
-        <v>19.885399176</v>
+        <v>19.769603808</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1091186601743472</v>
+        <v>0.1100927472971656</v>
       </c>
       <c r="T45">
-        <v>1.462324715342891</v>
+        <v>1.484820953745165</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.300650160721454</v>
+        <v>3.225635384341421</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08365105848641277</v>
+        <v>0.08360534067344763</v>
       </c>
       <c r="C46">
-        <v>107.1041425468872</v>
+        <v>104.9362787137393</v>
       </c>
       <c r="D46">
-        <v>206.2481425468872</v>
+        <v>206.3962787137393</v>
       </c>
       <c r="E46">
-        <v>-33.79599999999999</v>
+        <v>-31.47999999999999</v>
       </c>
       <c r="F46">
-        <v>101.904</v>
+        <v>104.22</v>
       </c>
       <c r="G46">
         <v>2.76</v>
@@ -5053,28 +5053,28 @@
         <v>21.07</v>
       </c>
       <c r="M46">
-        <v>6.5320464</v>
+        <v>6.680502000000001</v>
       </c>
       <c r="N46">
-        <v>14.5379536</v>
+        <v>14.389498</v>
       </c>
       <c r="O46">
-        <v>3.198349792</v>
+        <v>3.16568956</v>
       </c>
       <c r="P46">
-        <v>11.339603808</v>
+        <v>11.22380844</v>
       </c>
       <c r="Q46">
-        <v>19.769603808</v>
+        <v>19.65380844</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1100927472971656</v>
+        <v>0.1111022557699048</v>
       </c>
       <c r="T46">
-        <v>1.484820953745165</v>
+        <v>1.508135237180249</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.225635384341421</v>
+        <v>3.153954598022723</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08360534067344763</v>
+        <v>0.08355962286048249</v>
       </c>
       <c r="C47">
-        <v>104.9362787137393</v>
+        <v>102.7686278289004</v>
       </c>
       <c r="D47">
-        <v>206.3962787137393</v>
+        <v>206.5446278289004</v>
       </c>
       <c r="E47">
-        <v>-31.47999999999999</v>
+        <v>-29.16399999999999</v>
       </c>
       <c r="F47">
-        <v>104.22</v>
+        <v>106.536</v>
       </c>
       <c r="G47">
         <v>2.76</v>
@@ -5135,28 +5135,28 @@
         <v>21.07</v>
       </c>
       <c r="M47">
-        <v>6.680502000000001</v>
+        <v>6.828957600000001</v>
       </c>
       <c r="N47">
-        <v>14.389498</v>
+        <v>14.2410424</v>
       </c>
       <c r="O47">
-        <v>3.16568956</v>
+        <v>3.133029328</v>
       </c>
       <c r="P47">
-        <v>11.22380844</v>
+        <v>11.108013072</v>
       </c>
       <c r="Q47">
-        <v>19.65380844</v>
+        <v>19.538013072</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1111022557699048</v>
+        <v>0.1121491534453379</v>
       </c>
       <c r="T47">
-        <v>1.508135237180249</v>
+        <v>1.53231301259441</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.153954598022723</v>
+        <v>3.085390367630925</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08355962286048249</v>
+        <v>0.08351390504751736</v>
       </c>
       <c r="C48">
-        <v>102.7686278289004</v>
+        <v>100.6011903518762</v>
       </c>
       <c r="D48">
-        <v>206.5446278289004</v>
+        <v>206.6931903518762</v>
       </c>
       <c r="E48">
-        <v>-29.16399999999999</v>
+        <v>-26.84799999999998</v>
       </c>
       <c r="F48">
-        <v>106.536</v>
+        <v>108.852</v>
       </c>
       <c r="G48">
         <v>2.76</v>
@@ -5217,28 +5217,28 @@
         <v>21.07</v>
       </c>
       <c r="M48">
-        <v>6.828957600000001</v>
+        <v>6.977413200000001</v>
       </c>
       <c r="N48">
-        <v>14.2410424</v>
+        <v>14.0925868</v>
       </c>
       <c r="O48">
-        <v>3.133029328</v>
+        <v>3.100369096</v>
       </c>
       <c r="P48">
-        <v>11.108013072</v>
+        <v>10.992217704</v>
       </c>
       <c r="Q48">
-        <v>19.538013072</v>
+        <v>19.422217704</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1121491534453379</v>
+        <v>0.113235556693429</v>
       </c>
       <c r="T48">
-        <v>1.53231301259441</v>
+        <v>1.557403156892124</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.085390367630925</v>
+        <v>3.019743764064309</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08351390504751736</v>
+        <v>0.08638850723455223</v>
       </c>
       <c r="C49">
-        <v>100.6011903518762</v>
+        <v>89.34176977964233</v>
       </c>
       <c r="D49">
-        <v>206.6931903518762</v>
+        <v>197.7497697796423</v>
       </c>
       <c r="E49">
-        <v>-26.84799999999998</v>
+        <v>-24.53199999999998</v>
       </c>
       <c r="F49">
-        <v>108.852</v>
+        <v>111.168</v>
       </c>
       <c r="G49">
         <v>2.76</v>
@@ -5299,45 +5299,45 @@
         <v>21.07</v>
       </c>
       <c r="M49">
-        <v>6.977413200000001</v>
+        <v>7.992979200000002</v>
       </c>
       <c r="N49">
-        <v>14.0925868</v>
+        <v>13.0770208</v>
       </c>
       <c r="O49">
-        <v>3.100369096</v>
+        <v>2.876944576</v>
       </c>
       <c r="P49">
-        <v>10.992217704</v>
+        <v>10.200076224</v>
       </c>
       <c r="Q49">
-        <v>19.422217704</v>
+        <v>18.630076224</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.113235556693429</v>
+        <v>0.1143637446818312</v>
       </c>
       <c r="T49">
-        <v>1.557403156892124</v>
+        <v>1.583458306739751</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.22</v>
       </c>
       <c r="W49">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.019743764064309</v>
+        <v>2.636063409247956</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08638850723455223</v>
+        <v>0.08640362942158709</v>
       </c>
       <c r="C50">
-        <v>89.34176977964235</v>
+        <v>86.98076781418688</v>
       </c>
       <c r="D50">
-        <v>197.7497697796423</v>
+        <v>197.7047678141869</v>
       </c>
       <c r="E50">
-        <v>-24.532</v>
+        <v>-22.21599999999999</v>
       </c>
       <c r="F50">
-        <v>111.168</v>
+        <v>113.484</v>
       </c>
       <c r="G50">
         <v>2.76</v>
@@ -5381,28 +5381,28 @@
         <v>21.07</v>
       </c>
       <c r="M50">
-        <v>7.9929792</v>
+        <v>8.1594996</v>
       </c>
       <c r="N50">
-        <v>13.0770208</v>
+        <v>12.9105004</v>
       </c>
       <c r="O50">
-        <v>2.876944576</v>
+        <v>2.840310088</v>
       </c>
       <c r="P50">
-        <v>10.200076224</v>
+        <v>10.070190312</v>
       </c>
       <c r="Q50">
-        <v>18.630076224</v>
+        <v>18.500190312</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1143637446818312</v>
+        <v>0.1155361753364453</v>
       </c>
       <c r="T50">
-        <v>1.583458306739751</v>
+        <v>1.610535227169637</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.636063409247956</v>
+        <v>2.582266196814324</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08640362942158709</v>
+        <v>0.08641875160862195</v>
       </c>
       <c r="C51">
-        <v>86.98076781418688</v>
+        <v>84.61978632628889</v>
       </c>
       <c r="D51">
-        <v>197.7047678141869</v>
+        <v>197.6597863262889</v>
       </c>
       <c r="E51">
-        <v>-22.21599999999999</v>
+        <v>-19.89999999999999</v>
       </c>
       <c r="F51">
-        <v>113.484</v>
+        <v>115.8</v>
       </c>
       <c r="G51">
         <v>2.76</v>
@@ -5463,28 +5463,28 @@
         <v>21.07</v>
       </c>
       <c r="M51">
-        <v>8.1594996</v>
+        <v>8.32602</v>
       </c>
       <c r="N51">
-        <v>12.9105004</v>
+        <v>12.74398</v>
       </c>
       <c r="O51">
-        <v>2.840310088</v>
+        <v>2.8036756</v>
       </c>
       <c r="P51">
-        <v>10.070190312</v>
+        <v>9.9403044</v>
       </c>
       <c r="Q51">
-        <v>18.500190312</v>
+        <v>18.3703044</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1155361753364453</v>
+        <v>0.1167555032172439</v>
       </c>
       <c r="T51">
-        <v>1.610535227169637</v>
+        <v>1.638695224416719</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.582266196814324</v>
+        <v>2.530620872878038</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08641875160862195</v>
+        <v>0.08798529379565684</v>
       </c>
       <c r="C52">
-        <v>84.61978632628889</v>
+        <v>77.75238332190871</v>
       </c>
       <c r="D52">
-        <v>197.6597863262889</v>
+        <v>193.1083833219087</v>
       </c>
       <c r="E52">
-        <v>-19.89999999999999</v>
+        <v>-17.58399999999999</v>
       </c>
       <c r="F52">
-        <v>115.8</v>
+        <v>118.116</v>
       </c>
       <c r="G52">
         <v>2.76</v>
@@ -5545,45 +5545,45 @@
         <v>21.07</v>
       </c>
       <c r="M52">
-        <v>8.32602</v>
+        <v>8.9531928</v>
       </c>
       <c r="N52">
-        <v>12.74398</v>
+        <v>12.1168072</v>
       </c>
       <c r="O52">
-        <v>2.8036756</v>
+        <v>2.665697584</v>
       </c>
       <c r="P52">
-        <v>9.9403044</v>
+        <v>9.451109616</v>
       </c>
       <c r="Q52">
-        <v>18.3703044</v>
+        <v>17.881109616</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1167555032172439</v>
+        <v>0.1180245995829731</v>
       </c>
       <c r="T52">
-        <v>1.638695224416719</v>
+        <v>1.668004609306538</v>
       </c>
       <c r="U52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.22</v>
       </c>
       <c r="W52">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.530620872878038</v>
+        <v>2.353350415954407</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08798529379565684</v>
+        <v>0.08803083598269169</v>
       </c>
       <c r="C53">
-        <v>77.75238332190871</v>
+        <v>75.30719916425976</v>
       </c>
       <c r="D53">
-        <v>193.1083833219087</v>
+        <v>192.9791991642598</v>
       </c>
       <c r="E53">
-        <v>-17.58399999999999</v>
+        <v>-15.26799999999999</v>
       </c>
       <c r="F53">
-        <v>118.116</v>
+        <v>120.432</v>
       </c>
       <c r="G53">
         <v>2.76</v>
@@ -5627,28 +5627,28 @@
         <v>21.07</v>
       </c>
       <c r="M53">
-        <v>8.9531928</v>
+        <v>9.1287456</v>
       </c>
       <c r="N53">
-        <v>12.1168072</v>
+        <v>11.9412544</v>
       </c>
       <c r="O53">
-        <v>2.665697584</v>
+        <v>2.627075968</v>
       </c>
       <c r="P53">
-        <v>9.451109616</v>
+        <v>9.314178432</v>
       </c>
       <c r="Q53">
-        <v>17.881109616</v>
+        <v>17.744178432</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1180245995829731</v>
+        <v>0.119346574963941</v>
       </c>
       <c r="T53">
-        <v>1.668004609306538</v>
+        <v>1.698535218566767</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.353350415954407</v>
+        <v>2.308093677186053</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08803083598269169</v>
+        <v>0.08807637816972658</v>
       </c>
       <c r="C54">
-        <v>75.30719916425976</v>
+        <v>72.86218773230597</v>
       </c>
       <c r="D54">
-        <v>192.9791991642598</v>
+        <v>192.850187732306</v>
       </c>
       <c r="E54">
-        <v>-15.26799999999999</v>
+        <v>-12.95199999999998</v>
       </c>
       <c r="F54">
-        <v>120.432</v>
+        <v>122.748</v>
       </c>
       <c r="G54">
         <v>2.76</v>
@@ -5709,28 +5709,28 @@
         <v>21.07</v>
       </c>
       <c r="M54">
-        <v>9.1287456</v>
+        <v>9.3042984</v>
       </c>
       <c r="N54">
-        <v>11.9412544</v>
+        <v>11.7657016</v>
       </c>
       <c r="O54">
-        <v>2.627075968</v>
+        <v>2.588454352</v>
       </c>
       <c r="P54">
-        <v>9.314178432</v>
+        <v>9.177247248</v>
       </c>
       <c r="Q54">
-        <v>17.744178432</v>
+        <v>17.607247248</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.119346574963941</v>
+        <v>0.1207248046164395</v>
       </c>
       <c r="T54">
-        <v>1.698535218566767</v>
+        <v>1.730365002689134</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.308093677186053</v>
+        <v>2.264544739880655</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08807637816972658</v>
+        <v>0.08812192035676142</v>
       </c>
       <c r="C55">
-        <v>72.86218773230597</v>
+        <v>70.41734867986447</v>
       </c>
       <c r="D55">
-        <v>192.850187732306</v>
+        <v>192.7213486798645</v>
       </c>
       <c r="E55">
-        <v>-12.95199999999998</v>
+        <v>-10.63599999999998</v>
       </c>
       <c r="F55">
-        <v>122.748</v>
+        <v>125.064</v>
       </c>
       <c r="G55">
         <v>2.76</v>
@@ -5791,28 +5791,28 @@
         <v>21.07</v>
       </c>
       <c r="M55">
-        <v>9.3042984</v>
+        <v>9.479851200000001</v>
       </c>
       <c r="N55">
-        <v>11.7657016</v>
+        <v>11.5901488</v>
       </c>
       <c r="O55">
-        <v>2.588454352</v>
+        <v>2.549832736</v>
       </c>
       <c r="P55">
-        <v>9.177247248</v>
+        <v>9.040316063999999</v>
       </c>
       <c r="Q55">
-        <v>17.607247248</v>
+        <v>17.470316064</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1207248046164395</v>
+        <v>0.1221629572973074</v>
       </c>
       <c r="T55">
-        <v>1.730365002689134</v>
+        <v>1.763578690468994</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.264544739880655</v>
+        <v>2.222608726179162</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08812192035676142</v>
+        <v>0.08816746254379632</v>
       </c>
       <c r="C56">
-        <v>70.41734867986447</v>
+        <v>67.97268166167659</v>
       </c>
       <c r="D56">
-        <v>192.7213486798645</v>
+        <v>192.5926816616766</v>
       </c>
       <c r="E56">
-        <v>-10.63599999999998</v>
+        <v>-8.319999999999979</v>
       </c>
       <c r="F56">
-        <v>125.064</v>
+        <v>127.38</v>
       </c>
       <c r="G56">
         <v>2.76</v>
@@ -5873,28 +5873,28 @@
         <v>21.07</v>
       </c>
       <c r="M56">
-        <v>9.479851200000001</v>
+        <v>9.655404000000001</v>
       </c>
       <c r="N56">
-        <v>11.5901488</v>
+        <v>11.414596</v>
       </c>
       <c r="O56">
-        <v>2.549832736</v>
+        <v>2.51121112</v>
       </c>
       <c r="P56">
-        <v>9.040316063999999</v>
+        <v>8.903384879999999</v>
       </c>
       <c r="Q56">
-        <v>17.470316064</v>
+        <v>17.33338488</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1221629572973074</v>
+        <v>0.1236650278751029</v>
       </c>
       <c r="T56">
-        <v>1.763578690468994</v>
+        <v>1.798268542150182</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.222608726179162</v>
+        <v>2.18219765843045</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08816746254379632</v>
+        <v>0.08821300473083116</v>
       </c>
       <c r="C57">
-        <v>67.97268166167659</v>
+        <v>65.52818633340564</v>
       </c>
       <c r="D57">
-        <v>192.5926816616766</v>
+        <v>192.4641863334056</v>
       </c>
       <c r="E57">
-        <v>-8.319999999999979</v>
+        <v>-6.003999999999991</v>
       </c>
       <c r="F57">
-        <v>127.38</v>
+        <v>129.696</v>
       </c>
       <c r="G57">
         <v>2.76</v>
@@ -5955,28 +5955,28 @@
         <v>21.07</v>
       </c>
       <c r="M57">
-        <v>9.655404000000001</v>
+        <v>9.830956800000001</v>
       </c>
       <c r="N57">
-        <v>11.414596</v>
+        <v>11.2390432</v>
       </c>
       <c r="O57">
-        <v>2.51121112</v>
+        <v>2.472589504</v>
       </c>
       <c r="P57">
-        <v>8.903384879999999</v>
+        <v>8.766453695999999</v>
       </c>
       <c r="Q57">
-        <v>17.33338488</v>
+        <v>17.196453696</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1236650278751029</v>
+        <v>0.1252353743882526</v>
       </c>
       <c r="T57">
-        <v>1.798268542150182</v>
+        <v>1.834535205271424</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.18219765843045</v>
+        <v>2.143229843101334</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08821300473083116</v>
+        <v>0.08825854691786603</v>
       </c>
       <c r="C58">
-        <v>65.52818633340564</v>
+        <v>63.0838623516326</v>
       </c>
       <c r="D58">
-        <v>192.4641863334056</v>
+        <v>192.3358623516326</v>
       </c>
       <c r="E58">
-        <v>-6.003999999999991</v>
+        <v>-3.687999999999988</v>
       </c>
       <c r="F58">
-        <v>129.696</v>
+        <v>132.012</v>
       </c>
       <c r="G58">
         <v>2.76</v>
@@ -6037,28 +6037,28 @@
         <v>21.07</v>
       </c>
       <c r="M58">
-        <v>9.830956800000001</v>
+        <v>10.0065096</v>
       </c>
       <c r="N58">
-        <v>11.2390432</v>
+        <v>11.0634904</v>
       </c>
       <c r="O58">
-        <v>2.472589504</v>
+        <v>2.433967888</v>
       </c>
       <c r="P58">
-        <v>8.766453695999999</v>
+        <v>8.629522511999999</v>
       </c>
       <c r="Q58">
-        <v>17.196453696</v>
+        <v>17.059522512</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1252353743882526</v>
+        <v>0.126878760274107</v>
       </c>
       <c r="T58">
-        <v>1.834535205271424</v>
+        <v>1.872488689933188</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.143229843101334</v>
+        <v>2.105629319538153</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08825854691786603</v>
+        <v>0.0883040891049009</v>
       </c>
       <c r="C59">
-        <v>63.0838623516326</v>
+        <v>60.6397093738542</v>
       </c>
       <c r="D59">
-        <v>192.3358623516326</v>
+        <v>192.2077093738542</v>
       </c>
       <c r="E59">
-        <v>-3.687999999999988</v>
+        <v>-1.371999999999986</v>
       </c>
       <c r="F59">
-        <v>132.012</v>
+        <v>134.328</v>
       </c>
       <c r="G59">
         <v>2.76</v>
@@ -6119,28 +6119,28 @@
         <v>21.07</v>
       </c>
       <c r="M59">
-        <v>10.0065096</v>
+        <v>10.1820624</v>
       </c>
       <c r="N59">
-        <v>11.0634904</v>
+        <v>10.8879376</v>
       </c>
       <c r="O59">
-        <v>2.433967888</v>
+        <v>2.395346272</v>
       </c>
       <c r="P59">
-        <v>8.629522511999999</v>
+        <v>8.492591328</v>
       </c>
       <c r="Q59">
-        <v>17.059522512</v>
+        <v>16.922591328</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.126878760274107</v>
+        <v>0.1286004026307164</v>
       </c>
       <c r="T59">
-        <v>1.872488689933188</v>
+        <v>1.91224948338837</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.105629319538153</v>
+        <v>2.069325365753013</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0883040891049009</v>
+        <v>0.08834963129193577</v>
       </c>
       <c r="C60">
-        <v>60.63970937385423</v>
+        <v>58.19572705847926</v>
       </c>
       <c r="D60">
-        <v>192.2077093738542</v>
+        <v>192.0797270584792</v>
       </c>
       <c r="E60">
-        <v>-1.372000000000014</v>
+        <v>0.9439999999999884</v>
       </c>
       <c r="F60">
-        <v>134.328</v>
+        <v>136.644</v>
       </c>
       <c r="G60">
         <v>2.76</v>
@@ -6201,28 +6201,28 @@
         <v>21.07</v>
       </c>
       <c r="M60">
-        <v>10.1820624</v>
+        <v>10.3576152</v>
       </c>
       <c r="N60">
-        <v>10.8879376</v>
+        <v>10.7123848</v>
       </c>
       <c r="O60">
-        <v>2.395346272</v>
+        <v>2.356724656</v>
       </c>
       <c r="P60">
-        <v>8.492591328</v>
+        <v>8.355660144</v>
       </c>
       <c r="Q60">
-        <v>16.922591328</v>
+        <v>16.785660144</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1286004026307164</v>
+        <v>0.1304060275413067</v>
       </c>
       <c r="T60">
-        <v>1.91224948338837</v>
+        <v>1.953949827743804</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.069325365753013</v>
+        <v>2.034252054469063</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08834963129193577</v>
+        <v>0.08839517347897063</v>
       </c>
       <c r="C61">
-        <v>58.19572705847926</v>
+        <v>55.75191506482568</v>
       </c>
       <c r="D61">
-        <v>192.0797270584792</v>
+        <v>191.9519150648257</v>
       </c>
       <c r="E61">
-        <v>0.9439999999999884</v>
+        <v>3.259999999999991</v>
       </c>
       <c r="F61">
-        <v>136.644</v>
+        <v>138.96</v>
       </c>
       <c r="G61">
         <v>2.76</v>
@@ -6283,28 +6283,28 @@
         <v>21.07</v>
       </c>
       <c r="M61">
-        <v>10.3576152</v>
+        <v>10.533168</v>
       </c>
       <c r="N61">
-        <v>10.7123848</v>
+        <v>10.536832</v>
       </c>
       <c r="O61">
-        <v>2.356724656</v>
+        <v>2.31810304</v>
       </c>
       <c r="P61">
-        <v>8.355660144</v>
+        <v>8.21872896</v>
       </c>
       <c r="Q61">
-        <v>16.785660144</v>
+        <v>16.64872896</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1304060275413067</v>
+        <v>0.1323019336974266</v>
       </c>
       <c r="T61">
-        <v>1.953949827743804</v>
+        <v>1.997735189317011</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.034252054469063</v>
+        <v>2.000347853561246</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08839517347897063</v>
+        <v>0.09519707566600549</v>
       </c>
       <c r="C62">
-        <v>55.75191506482568</v>
+        <v>36.08387624429798</v>
       </c>
       <c r="D62">
-        <v>191.9519150648257</v>
+        <v>174.599876244298</v>
       </c>
       <c r="E62">
-        <v>3.259999999999991</v>
+        <v>5.575999999999993</v>
       </c>
       <c r="F62">
-        <v>138.96</v>
+        <v>141.276</v>
       </c>
       <c r="G62">
         <v>2.76</v>
@@ -6365,45 +6365,45 @@
         <v>21.07</v>
       </c>
       <c r="M62">
-        <v>10.533168</v>
+        <v>12.71484</v>
       </c>
       <c r="N62">
-        <v>10.536832</v>
+        <v>8.355160000000003</v>
       </c>
       <c r="O62">
-        <v>2.31810304</v>
+        <v>1.838135200000001</v>
       </c>
       <c r="P62">
-        <v>8.21872896</v>
+        <v>6.517024800000002</v>
       </c>
       <c r="Q62">
-        <v>16.64872896</v>
+        <v>14.9470248</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1323019336974266</v>
+        <v>0.1342950658102705</v>
       </c>
       <c r="T62">
-        <v>1.997735189317011</v>
+        <v>2.043765954047817</v>
       </c>
       <c r="U62">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V62">
         <v>0.22</v>
       </c>
       <c r="W62">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.000347853561246</v>
+        <v>1.657118768305382</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09519707566600549</v>
+        <v>0.09535337785304035</v>
       </c>
       <c r="C63">
-        <v>36.08387624429798</v>
+        <v>33.40593718395147</v>
       </c>
       <c r="D63">
-        <v>174.599876244298</v>
+        <v>174.2379371839515</v>
       </c>
       <c r="E63">
-        <v>5.575999999999993</v>
+        <v>7.891999999999996</v>
       </c>
       <c r="F63">
-        <v>141.276</v>
+        <v>143.592</v>
       </c>
       <c r="G63">
         <v>2.76</v>
@@ -6447,28 +6447,28 @@
         <v>21.07</v>
       </c>
       <c r="M63">
-        <v>12.71484</v>
+        <v>12.92328</v>
       </c>
       <c r="N63">
-        <v>8.355160000000003</v>
+        <v>8.146720000000002</v>
       </c>
       <c r="O63">
-        <v>1.838135200000001</v>
+        <v>1.7922784</v>
       </c>
       <c r="P63">
-        <v>6.517024800000002</v>
+        <v>6.354441600000001</v>
       </c>
       <c r="Q63">
-        <v>14.9470248</v>
+        <v>14.7844416</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1342950658102705</v>
+        <v>0.1363930996132641</v>
       </c>
       <c r="T63">
-        <v>2.043765954047817</v>
+        <v>2.092219390606561</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.657118768305382</v>
+        <v>1.63039104623594</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09535337785304035</v>
+        <v>0.09550968004007522</v>
       </c>
       <c r="C64">
-        <v>33.40593718395147</v>
+        <v>30.72949559187455</v>
       </c>
       <c r="D64">
-        <v>174.2379371839515</v>
+        <v>173.8774955918745</v>
       </c>
       <c r="E64">
-        <v>7.891999999999996</v>
+        <v>10.208</v>
       </c>
       <c r="F64">
-        <v>143.592</v>
+        <v>145.908</v>
       </c>
       <c r="G64">
         <v>2.76</v>
@@ -6529,28 +6529,28 @@
         <v>21.07</v>
       </c>
       <c r="M64">
-        <v>12.92328</v>
+        <v>13.13172</v>
       </c>
       <c r="N64">
-        <v>8.146720000000002</v>
+        <v>7.938280000000002</v>
       </c>
       <c r="O64">
-        <v>1.7922784</v>
+        <v>1.746421600000001</v>
       </c>
       <c r="P64">
-        <v>6.354441600000001</v>
+        <v>6.191858400000002</v>
       </c>
       <c r="Q64">
-        <v>14.7844416</v>
+        <v>14.6218584</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1363930996132641</v>
+        <v>0.1386045406488519</v>
       </c>
       <c r="T64">
-        <v>2.092219390606561</v>
+        <v>2.143291931844156</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.63039104623594</v>
+        <v>1.604511823279814</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09550968004007522</v>
+        <v>0.09566598222711009</v>
       </c>
       <c r="C65">
-        <v>30.72949559187455</v>
+        <v>28.05454219392874</v>
       </c>
       <c r="D65">
-        <v>173.8774955918745</v>
+        <v>173.5185421939287</v>
       </c>
       <c r="E65">
-        <v>10.208</v>
+        <v>12.524</v>
       </c>
       <c r="F65">
-        <v>145.908</v>
+        <v>148.224</v>
       </c>
       <c r="G65">
         <v>2.76</v>
@@ -6611,28 +6611,28 @@
         <v>21.07</v>
       </c>
       <c r="M65">
-        <v>13.13172</v>
+        <v>13.34016</v>
       </c>
       <c r="N65">
-        <v>7.938280000000002</v>
+        <v>7.729840000000001</v>
       </c>
       <c r="O65">
-        <v>1.746421600000001</v>
+        <v>1.7005648</v>
       </c>
       <c r="P65">
-        <v>6.191858400000002</v>
+        <v>6.029275200000001</v>
       </c>
       <c r="Q65">
-        <v>14.6218584</v>
+        <v>14.4592752</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1386045406488519</v>
+        <v>0.1409388395197503</v>
       </c>
       <c r="T65">
-        <v>2.143291931844156</v>
+        <v>2.19720183648384</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.604511823279814</v>
+        <v>1.579441326041067</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09566598222711009</v>
+        <v>0.09582228441414496</v>
       </c>
       <c r="C66">
-        <v>28.05454219392874</v>
+        <v>25.38106779240007</v>
       </c>
       <c r="D66">
-        <v>173.5185421939287</v>
+        <v>173.1610677924001</v>
       </c>
       <c r="E66">
-        <v>12.524</v>
+        <v>14.84</v>
       </c>
       <c r="F66">
-        <v>148.224</v>
+        <v>150.54</v>
       </c>
       <c r="G66">
         <v>2.76</v>
@@ -6693,28 +6693,28 @@
         <v>21.07</v>
       </c>
       <c r="M66">
-        <v>13.34016</v>
+        <v>13.5486</v>
       </c>
       <c r="N66">
-        <v>7.729840000000001</v>
+        <v>7.521400000000002</v>
       </c>
       <c r="O66">
-        <v>1.7005648</v>
+        <v>1.654708</v>
       </c>
       <c r="P66">
-        <v>6.029275200000001</v>
+        <v>5.866692000000001</v>
       </c>
       <c r="Q66">
-        <v>14.4592752</v>
+        <v>14.296692</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1409388395197503</v>
+        <v>0.143406526897557</v>
       </c>
       <c r="T66">
-        <v>2.19720183648384</v>
+        <v>2.254192307102934</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.579441326041067</v>
+        <v>1.555142228717358</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09582228441414496</v>
+        <v>0.09597858660117983</v>
       </c>
       <c r="C67">
-        <v>25.38106779240007</v>
+        <v>22.7090632652135</v>
       </c>
       <c r="D67">
-        <v>173.1610677924001</v>
+        <v>172.8050632652135</v>
       </c>
       <c r="E67">
-        <v>14.84</v>
+        <v>17.15600000000001</v>
       </c>
       <c r="F67">
-        <v>150.54</v>
+        <v>152.856</v>
       </c>
       <c r="G67">
         <v>2.76</v>
@@ -6775,28 +6775,28 @@
         <v>21.07</v>
       </c>
       <c r="M67">
-        <v>13.5486</v>
+        <v>13.75704</v>
       </c>
       <c r="N67">
-        <v>7.521400000000002</v>
+        <v>7.312960000000002</v>
       </c>
       <c r="O67">
-        <v>1.654708</v>
+        <v>1.6088512</v>
       </c>
       <c r="P67">
-        <v>5.866692000000001</v>
+        <v>5.704108800000002</v>
       </c>
       <c r="Q67">
-        <v>14.296692</v>
+        <v>14.1341088</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.143406526897557</v>
+        <v>0.1460193723564113</v>
       </c>
       <c r="T67">
-        <v>2.254192307102934</v>
+        <v>2.314535158346681</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.555142228717358</v>
+        <v>1.531579467676186</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09597858660117983</v>
+        <v>0.09613488878821469</v>
       </c>
       <c r="C68">
-        <v>22.7090632652135</v>
+        <v>20.03851956515692</v>
       </c>
       <c r="D68">
-        <v>172.8050632652135</v>
+        <v>172.4505195651569</v>
       </c>
       <c r="E68">
-        <v>17.15600000000001</v>
+        <v>19.47200000000001</v>
       </c>
       <c r="F68">
-        <v>152.856</v>
+        <v>155.172</v>
       </c>
       <c r="G68">
         <v>2.76</v>
@@ -6857,28 +6857,28 @@
         <v>21.07</v>
       </c>
       <c r="M68">
-        <v>13.75704</v>
+        <v>13.96548</v>
       </c>
       <c r="N68">
-        <v>7.312960000000002</v>
+        <v>7.104520000000001</v>
       </c>
       <c r="O68">
-        <v>1.6088512</v>
+        <v>1.5629944</v>
       </c>
       <c r="P68">
-        <v>5.704108800000002</v>
+        <v>5.541525600000001</v>
       </c>
       <c r="Q68">
-        <v>14.1341088</v>
+        <v>13.9715256</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1460193723564113</v>
+        <v>0.1487905720854991</v>
       </c>
       <c r="T68">
-        <v>2.314535158346681</v>
+        <v>2.378535152090048</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.531579467676186</v>
+        <v>1.508720072636243</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09613488878821469</v>
+        <v>0.1288930976860711</v>
       </c>
       <c r="C69">
-        <v>20.03851956515692</v>
+        <v>-34.13322664806056</v>
       </c>
       <c r="D69">
-        <v>172.4505195651569</v>
+        <v>120.5947733519394</v>
       </c>
       <c r="E69">
-        <v>19.47200000000001</v>
+        <v>21.78800000000001</v>
       </c>
       <c r="F69">
-        <v>155.172</v>
+        <v>157.488</v>
       </c>
       <c r="G69">
         <v>2.76</v>
@@ -6939,45 +6939,45 @@
         <v>21.07</v>
       </c>
       <c r="M69">
-        <v>13.96548</v>
+        <v>23.1192384</v>
       </c>
       <c r="N69">
-        <v>7.104520000000001</v>
+        <v>-2.0492384</v>
       </c>
       <c r="O69">
-        <v>1.5629944</v>
+        <v>-0.4508324480000001</v>
       </c>
       <c r="P69">
-        <v>5.541525600000001</v>
+        <v>-1.598405952</v>
       </c>
       <c r="Q69">
-        <v>13.9715256</v>
+        <v>6.831594047999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1487905720854991</v>
+        <v>0.1533868067801985</v>
       </c>
       <c r="T69">
-        <v>2.378535152090048</v>
+        <v>2.484683759357933</v>
       </c>
       <c r="U69">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.22</v>
+        <v>0.2004996842802573</v>
       </c>
       <c r="W69">
-        <v>0.0702</v>
+        <v>0.1173666463476582</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.508720072636243</v>
+        <v>0.9113622012738967</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1288930976860711</v>
+        <v>0.1299030976860711</v>
       </c>
       <c r="C70">
-        <v>-34.13322664806056</v>
+        <v>-37.55700846729393</v>
       </c>
       <c r="D70">
-        <v>120.5947733519394</v>
+        <v>119.4869915327061</v>
       </c>
       <c r="E70">
-        <v>21.78800000000001</v>
+        <v>24.10400000000001</v>
       </c>
       <c r="F70">
-        <v>157.488</v>
+        <v>159.804</v>
       </c>
       <c r="G70">
         <v>2.76</v>
@@ -7021,37 +7021,37 @@
         <v>21.07</v>
       </c>
       <c r="M70">
-        <v>23.1192384</v>
+        <v>23.4592272</v>
       </c>
       <c r="N70">
-        <v>-2.0492384</v>
+        <v>-2.389227200000001</v>
       </c>
       <c r="O70">
-        <v>-0.4508324480000001</v>
+        <v>-0.5256299840000002</v>
       </c>
       <c r="P70">
-        <v>-1.598405952</v>
+        <v>-1.863597216000001</v>
       </c>
       <c r="Q70">
-        <v>6.831594047999999</v>
+        <v>6.566402783999999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1533868067801985</v>
+        <v>0.1568573489343985</v>
       </c>
       <c r="T70">
-        <v>2.484683759357933</v>
+        <v>2.56483484836948</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2004996842802573</v>
+        <v>0.1975938917544564</v>
       </c>
       <c r="W70">
-        <v>0.1173666463476582</v>
+        <v>0.1177932166904458</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9113622012738967</v>
+        <v>0.8981540534293474</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1299030976860711</v>
+        <v>0.1309130976860711</v>
       </c>
       <c r="C71">
-        <v>-37.55700846729393</v>
+        <v>-40.96062340412617</v>
       </c>
       <c r="D71">
-        <v>119.4869915327061</v>
+        <v>118.3993765958738</v>
       </c>
       <c r="E71">
-        <v>24.10400000000001</v>
+        <v>26.42000000000002</v>
       </c>
       <c r="F71">
-        <v>159.804</v>
+        <v>162.12</v>
       </c>
       <c r="G71">
         <v>2.76</v>
@@ -7103,37 +7103,37 @@
         <v>21.07</v>
       </c>
       <c r="M71">
-        <v>23.4592272</v>
+        <v>23.799216</v>
       </c>
       <c r="N71">
-        <v>-2.389227200000001</v>
+        <v>-2.729216000000001</v>
       </c>
       <c r="O71">
-        <v>-0.5256299840000002</v>
+        <v>-0.6004275200000002</v>
       </c>
       <c r="P71">
-        <v>-1.863597216000001</v>
+        <v>-2.128788480000001</v>
       </c>
       <c r="Q71">
-        <v>6.566402783999999</v>
+        <v>6.301211519999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1568573489343985</v>
+        <v>0.1605592605655451</v>
       </c>
       <c r="T71">
-        <v>2.56483484836948</v>
+        <v>2.650329343315129</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1975938917544564</v>
+        <v>0.1947711218722499</v>
       </c>
       <c r="W71">
-        <v>0.1177932166904458</v>
+        <v>0.1182075993091537</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8981540534293474</v>
+        <v>0.8853232812374996</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1309130976860711</v>
+        <v>0.1319230976860711</v>
       </c>
       <c r="C72">
-        <v>-40.96062340412617</v>
+        <v>-44.34461719044498</v>
       </c>
       <c r="D72">
-        <v>118.3993765958738</v>
+        <v>117.331382809555</v>
       </c>
       <c r="E72">
-        <v>26.42000000000002</v>
+        <v>28.73600000000002</v>
       </c>
       <c r="F72">
-        <v>162.12</v>
+        <v>164.436</v>
       </c>
       <c r="G72">
         <v>2.76</v>
@@ -7185,37 +7185,37 @@
         <v>21.07</v>
       </c>
       <c r="M72">
-        <v>23.799216</v>
+        <v>24.1392048</v>
       </c>
       <c r="N72">
-        <v>-2.729216000000001</v>
+        <v>-3.069204800000001</v>
       </c>
       <c r="O72">
-        <v>-0.6004275200000002</v>
+        <v>-0.6752250560000003</v>
       </c>
       <c r="P72">
-        <v>-2.128788480000001</v>
+        <v>-2.393979744000001</v>
       </c>
       <c r="Q72">
-        <v>6.301211519999999</v>
+        <v>6.036020255999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1605592605655451</v>
+        <v>0.1645164764471156</v>
       </c>
       <c r="T72">
-        <v>2.650329343315129</v>
+        <v>2.741720010325996</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1947711218722499</v>
+        <v>0.1920278666346126</v>
       </c>
       <c r="W72">
-        <v>0.1182075993091537</v>
+        <v>0.1186103091780389</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8853232812374996</v>
+        <v>0.872853939248239</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1319230976860711</v>
+        <v>0.1329330976860711</v>
       </c>
       <c r="C73">
-        <v>-44.34461719044495</v>
+        <v>-47.70951604357877</v>
       </c>
       <c r="D73">
-        <v>117.331382809555</v>
+        <v>116.2824839564212</v>
       </c>
       <c r="E73">
-        <v>28.73599999999999</v>
+        <v>31.05199999999999</v>
       </c>
       <c r="F73">
-        <v>164.436</v>
+        <v>166.752</v>
       </c>
       <c r="G73">
         <v>2.76</v>
@@ -7267,37 +7267,37 @@
         <v>21.07</v>
       </c>
       <c r="M73">
-        <v>24.1392048</v>
+        <v>24.4791936</v>
       </c>
       <c r="N73">
-        <v>-3.069204799999998</v>
+        <v>-3.409193599999998</v>
       </c>
       <c r="O73">
-        <v>-0.6752250559999995</v>
+        <v>-0.7500225919999997</v>
       </c>
       <c r="P73">
-        <v>-2.393979743999998</v>
+        <v>-2.659171007999999</v>
       </c>
       <c r="Q73">
-        <v>6.036020256000001</v>
+        <v>5.770828992000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1645164764471156</v>
+        <v>0.1687563506059411</v>
       </c>
       <c r="T73">
-        <v>2.741720010325995</v>
+        <v>2.839638582123352</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1920278666346126</v>
+        <v>0.1893608129313541</v>
       </c>
       <c r="W73">
-        <v>0.1186103091780389</v>
+        <v>0.1190018326616772</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8728539392482391</v>
+        <v>0.8607309678697913</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1329330976860711</v>
+        <v>0.1339430976860711</v>
       </c>
       <c r="C74">
-        <v>-47.70951604357877</v>
+        <v>-51.05582753083291</v>
       </c>
       <c r="D74">
-        <v>116.2824839564212</v>
+        <v>115.2521724691671</v>
       </c>
       <c r="E74">
-        <v>31.05199999999999</v>
+        <v>33.36799999999999</v>
       </c>
       <c r="F74">
-        <v>166.752</v>
+        <v>169.068</v>
       </c>
       <c r="G74">
         <v>2.76</v>
@@ -7349,37 +7349,37 @@
         <v>21.07</v>
       </c>
       <c r="M74">
-        <v>24.4791936</v>
+        <v>24.8191824</v>
       </c>
       <c r="N74">
-        <v>-3.409193599999998</v>
+        <v>-3.749182399999999</v>
       </c>
       <c r="O74">
-        <v>-0.7500225919999997</v>
+        <v>-0.8248201279999997</v>
       </c>
       <c r="P74">
-        <v>-2.659171007999999</v>
+        <v>-2.924362271999999</v>
       </c>
       <c r="Q74">
-        <v>5.770828992000001</v>
+        <v>5.505637728000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1687563506059411</v>
+        <v>0.1733102895172723</v>
       </c>
       <c r="T74">
-        <v>2.839638582123352</v>
+        <v>2.944810381461254</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1893608129313541</v>
+        <v>0.1867668291925684</v>
       </c>
       <c r="W74">
-        <v>0.1190018326616772</v>
+        <v>0.119382629474531</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8607309678697913</v>
+        <v>0.8489401326934928</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1339430976860711</v>
+        <v>0.1349530976860711</v>
       </c>
       <c r="C75">
-        <v>-51.05582753083291</v>
+        <v>-54.38404138846776</v>
       </c>
       <c r="D75">
-        <v>115.2521724691671</v>
+        <v>114.2399586115322</v>
       </c>
       <c r="E75">
-        <v>33.36799999999999</v>
+        <v>35.684</v>
       </c>
       <c r="F75">
-        <v>169.068</v>
+        <v>171.384</v>
       </c>
       <c r="G75">
         <v>2.76</v>
@@ -7431,37 +7431,37 @@
         <v>21.07</v>
       </c>
       <c r="M75">
-        <v>24.8191824</v>
+        <v>25.1591712</v>
       </c>
       <c r="N75">
-        <v>-3.749182399999999</v>
+        <v>-4.089171199999999</v>
       </c>
       <c r="O75">
-        <v>-0.8248201279999997</v>
+        <v>-0.8996176639999998</v>
       </c>
       <c r="P75">
-        <v>-2.924362271999999</v>
+        <v>-3.189553535999999</v>
       </c>
       <c r="Q75">
-        <v>5.505637728000001</v>
+        <v>5.240446464000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1733102895172723</v>
+        <v>0.1782145314217828</v>
       </c>
       <c r="T75">
-        <v>2.944810381461254</v>
+        <v>3.058072319209764</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1867668291925684</v>
+        <v>0.1842429531223986</v>
       </c>
       <c r="W75">
-        <v>0.119382629474531</v>
+        <v>0.1197531344816319</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8489401326934928</v>
+        <v>0.8374679687381753</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1349530976860711</v>
+        <v>0.1359630976860711</v>
       </c>
       <c r="C76">
-        <v>-54.38404138846776</v>
+        <v>-57.69463029789698</v>
       </c>
       <c r="D76">
-        <v>114.2399586115322</v>
+        <v>113.245369702103</v>
       </c>
       <c r="E76">
-        <v>35.684</v>
+        <v>38</v>
       </c>
       <c r="F76">
-        <v>171.384</v>
+        <v>173.7</v>
       </c>
       <c r="G76">
         <v>2.76</v>
@@ -7513,37 +7513,37 @@
         <v>21.07</v>
       </c>
       <c r="M76">
-        <v>25.1591712</v>
+        <v>25.49916</v>
       </c>
       <c r="N76">
-        <v>-4.089171199999999</v>
+        <v>-4.42916</v>
       </c>
       <c r="O76">
-        <v>-0.8996176639999998</v>
+        <v>-0.9744151999999999</v>
       </c>
       <c r="P76">
-        <v>-3.189553535999999</v>
+        <v>-3.454744799999999</v>
       </c>
       <c r="Q76">
-        <v>5.240446464000001</v>
+        <v>4.9752552</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1782145314217828</v>
+        <v>0.1835111126786541</v>
       </c>
       <c r="T76">
-        <v>3.058072319209764</v>
+        <v>3.180395211978154</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1842429531223986</v>
+        <v>0.1817863804140999</v>
       </c>
       <c r="W76">
-        <v>0.1197531344816319</v>
+        <v>0.1201137593552102</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8374679687381753</v>
+        <v>0.8263017291549997</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1359630976860711</v>
+        <v>0.1369730976860711</v>
       </c>
       <c r="C77">
-        <v>-57.69463029789698</v>
+        <v>-60.98805062168863</v>
       </c>
       <c r="D77">
-        <v>113.245369702103</v>
+        <v>112.2679493783114</v>
       </c>
       <c r="E77">
-        <v>38</v>
+        <v>40.316</v>
       </c>
       <c r="F77">
-        <v>173.7</v>
+        <v>176.016</v>
       </c>
       <c r="G77">
         <v>2.76</v>
@@ -7595,37 +7595,37 @@
         <v>21.07</v>
       </c>
       <c r="M77">
-        <v>25.49916</v>
+        <v>25.8391488</v>
       </c>
       <c r="N77">
-        <v>-4.42916</v>
+        <v>-4.7691488</v>
       </c>
       <c r="O77">
-        <v>-0.9744151999999999</v>
+        <v>-1.049212736</v>
       </c>
       <c r="P77">
-        <v>-3.454744799999999</v>
+        <v>-3.719936064</v>
       </c>
       <c r="Q77">
-        <v>4.9752552</v>
+        <v>4.710063936</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1835111126786541</v>
+        <v>0.1892490757069314</v>
       </c>
       <c r="T77">
-        <v>3.180395211978154</v>
+        <v>3.312911679143911</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1817863804140999</v>
+        <v>0.1793944543560197</v>
       </c>
       <c r="W77">
-        <v>0.1201137593552102</v>
+        <v>0.1204648941005363</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8263017291549997</v>
+        <v>0.8154293379819075</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1369730976860711</v>
+        <v>0.1379830976860711</v>
       </c>
       <c r="C78">
-        <v>-60.98805062168863</v>
+        <v>-64.26474310177859</v>
       </c>
       <c r="D78">
-        <v>112.2679493783114</v>
+        <v>111.3072568982214</v>
       </c>
       <c r="E78">
-        <v>40.316</v>
+        <v>42.63200000000001</v>
       </c>
       <c r="F78">
-        <v>176.016</v>
+        <v>178.332</v>
       </c>
       <c r="G78">
         <v>2.76</v>
@@ -7677,37 +7677,37 @@
         <v>21.07</v>
       </c>
       <c r="M78">
-        <v>25.8391488</v>
+        <v>26.1791376</v>
       </c>
       <c r="N78">
-        <v>-4.7691488</v>
+        <v>-5.1091376</v>
       </c>
       <c r="O78">
-        <v>-1.049212736</v>
+        <v>-1.124010272</v>
       </c>
       <c r="P78">
-        <v>-3.719936064</v>
+        <v>-3.985127328</v>
       </c>
       <c r="Q78">
-        <v>4.710063936</v>
+        <v>4.444872671999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1892490757069314</v>
+        <v>0.1954859920420153</v>
       </c>
       <c r="T78">
-        <v>3.312911679143911</v>
+        <v>3.456951317367559</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1793944543560197</v>
+        <v>0.1770646562474999</v>
       </c>
       <c r="W78">
-        <v>0.1204648941005363</v>
+        <v>0.120806908462867</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8154293379819075</v>
+        <v>0.804839346579545</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1379830976860711</v>
+        <v>0.1825746647214775</v>
       </c>
       <c r="C79">
-        <v>-64.26474310177859</v>
+        <v>-97.10167624526812</v>
       </c>
       <c r="D79">
-        <v>111.3072568982214</v>
+        <v>80.78632375473187</v>
       </c>
       <c r="E79">
-        <v>42.63200000000001</v>
+        <v>44.94800000000001</v>
       </c>
       <c r="F79">
-        <v>178.332</v>
+        <v>180.648</v>
       </c>
       <c r="G79">
         <v>2.76</v>
@@ -7759,45 +7759,45 @@
         <v>21.07</v>
       </c>
       <c r="M79">
-        <v>26.1791376</v>
+        <v>36.2741184</v>
       </c>
       <c r="N79">
-        <v>-5.1091376</v>
+        <v>-15.2041184</v>
       </c>
       <c r="O79">
-        <v>-1.124010272</v>
+        <v>-3.344906048</v>
       </c>
       <c r="P79">
-        <v>-3.985127328</v>
+        <v>-11.859212352</v>
       </c>
       <c r="Q79">
-        <v>4.444872671999999</v>
+        <v>-3.429212351999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1954859920420153</v>
+        <v>0.2089333872957726</v>
       </c>
       <c r="T79">
-        <v>3.456951317367559</v>
+        <v>3.767514718147173</v>
       </c>
       <c r="U79">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1770646562474999</v>
+        <v>0.12778808154301</v>
       </c>
       <c r="W79">
-        <v>0.120806908462867</v>
+        <v>0.1751401532261636</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.804839346579545</v>
+        <v>0.5808549161045911</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1825746647214775</v>
+        <v>0.1841246647214776</v>
       </c>
       <c r="C80">
-        <v>-97.10167624526812</v>
+        <v>-100.1804071389418</v>
       </c>
       <c r="D80">
-        <v>80.78632375473187</v>
+        <v>80.02359286105823</v>
       </c>
       <c r="E80">
-        <v>44.94800000000001</v>
+        <v>47.26400000000001</v>
       </c>
       <c r="F80">
-        <v>180.648</v>
+        <v>182.964</v>
       </c>
       <c r="G80">
         <v>2.76</v>
@@ -7841,37 +7841,37 @@
         <v>21.07</v>
       </c>
       <c r="M80">
-        <v>36.2741184</v>
+        <v>36.7391712</v>
       </c>
       <c r="N80">
-        <v>-15.2041184</v>
+        <v>-15.6691712</v>
       </c>
       <c r="O80">
-        <v>-3.344906048</v>
+        <v>-3.447217664</v>
       </c>
       <c r="P80">
-        <v>-11.859212352</v>
+        <v>-12.221953536</v>
       </c>
       <c r="Q80">
-        <v>-3.429212351999999</v>
+        <v>-3.791953536000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2089333872957726</v>
+        <v>0.2167016438336666</v>
       </c>
       <c r="T80">
-        <v>3.767514718147173</v>
+        <v>3.946920180916087</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.12778808154301</v>
+        <v>0.1261705108905669</v>
       </c>
       <c r="W80">
-        <v>0.1751401532261636</v>
+        <v>0.1754649614131742</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5808549161045911</v>
+        <v>0.5735023222298493</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1841246647214776</v>
+        <v>0.1856746647214776</v>
       </c>
       <c r="C81">
-        <v>-100.1804071389418</v>
+        <v>-103.2448703401529</v>
       </c>
       <c r="D81">
-        <v>80.02359286105823</v>
+        <v>79.2751296598471</v>
       </c>
       <c r="E81">
-        <v>47.26400000000001</v>
+        <v>49.58000000000001</v>
       </c>
       <c r="F81">
-        <v>182.964</v>
+        <v>185.28</v>
       </c>
       <c r="G81">
         <v>2.76</v>
@@ -7923,37 +7923,37 @@
         <v>21.07</v>
       </c>
       <c r="M81">
-        <v>36.7391712</v>
+        <v>37.204224</v>
       </c>
       <c r="N81">
-        <v>-15.6691712</v>
+        <v>-16.134224</v>
       </c>
       <c r="O81">
-        <v>-3.447217664</v>
+        <v>-3.549529280000001</v>
       </c>
       <c r="P81">
-        <v>-12.221953536</v>
+        <v>-12.58469472</v>
       </c>
       <c r="Q81">
-        <v>-3.791953536000001</v>
+        <v>-4.154694720000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2167016438336666</v>
+        <v>0.2252467260253499</v>
       </c>
       <c r="T81">
-        <v>3.946920180916087</v>
+        <v>4.144266189961891</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1261705108905669</v>
+        <v>0.1245933795044347</v>
       </c>
       <c r="W81">
-        <v>0.1754649614131742</v>
+        <v>0.1757816493955095</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5735023222298493</v>
+        <v>0.5663335432019762</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1856746647214776</v>
+        <v>0.1872246647214776</v>
       </c>
       <c r="C82">
-        <v>-103.2448703401529</v>
+        <v>-106.2954624777592</v>
       </c>
       <c r="D82">
-        <v>79.2751296598471</v>
+        <v>78.54053752224084</v>
       </c>
       <c r="E82">
-        <v>49.58000000000001</v>
+        <v>51.89600000000002</v>
       </c>
       <c r="F82">
-        <v>185.28</v>
+        <v>187.596</v>
       </c>
       <c r="G82">
         <v>2.76</v>
@@ -8005,37 +8005,37 @@
         <v>21.07</v>
       </c>
       <c r="M82">
-        <v>37.204224</v>
+        <v>37.6692768</v>
       </c>
       <c r="N82">
-        <v>-16.134224</v>
+        <v>-16.5992768</v>
       </c>
       <c r="O82">
-        <v>-3.549529280000001</v>
+        <v>-3.651840896</v>
       </c>
       <c r="P82">
-        <v>-12.58469472</v>
+        <v>-12.947435904</v>
       </c>
       <c r="Q82">
-        <v>-4.154694720000002</v>
+        <v>-4.517435903999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2252467260253499</v>
+        <v>0.2346912905529999</v>
       </c>
       <c r="T82">
-        <v>4.144266189961891</v>
+        <v>4.36238546311778</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1245933795044347</v>
+        <v>0.1230551896340096</v>
       </c>
       <c r="W82">
-        <v>0.1757816493955095</v>
+        <v>0.1760905179214909</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5663335432019762</v>
+        <v>0.5593417710636802</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1872246647214776</v>
+        <v>0.1887746647214776</v>
       </c>
       <c r="C83">
-        <v>-106.2954624777592</v>
+        <v>-109.3325656143663</v>
       </c>
       <c r="D83">
-        <v>78.54053752224084</v>
+        <v>77.81943438563367</v>
       </c>
       <c r="E83">
-        <v>51.89600000000002</v>
+        <v>54.21200000000002</v>
       </c>
       <c r="F83">
-        <v>187.596</v>
+        <v>189.912</v>
       </c>
       <c r="G83">
         <v>2.76</v>
@@ -8087,37 +8087,37 @@
         <v>21.07</v>
       </c>
       <c r="M83">
-        <v>37.6692768</v>
+        <v>38.1343296</v>
       </c>
       <c r="N83">
-        <v>-16.5992768</v>
+        <v>-17.0643296</v>
       </c>
       <c r="O83">
-        <v>-3.651840896</v>
+        <v>-3.754152512</v>
       </c>
       <c r="P83">
-        <v>-12.947435904</v>
+        <v>-13.310177088</v>
       </c>
       <c r="Q83">
-        <v>-4.517435903999999</v>
+        <v>-4.880177088</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2346912905529999</v>
+        <v>0.2451852511392777</v>
       </c>
       <c r="T83">
-        <v>4.36238546311778</v>
+        <v>4.604740211068768</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1230551896340096</v>
+        <v>0.1215545165896924</v>
       </c>
       <c r="W83">
-        <v>0.1760905179214909</v>
+        <v>0.1763918530687898</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5593417710636802</v>
+        <v>0.5525205299531475</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1887746647214776</v>
+        <v>0.1903246647214776</v>
       </c>
       <c r="C84">
-        <v>-109.3325656143663</v>
+        <v>-112.3565479089293</v>
       </c>
       <c r="D84">
-        <v>77.81943438563367</v>
+        <v>77.11145209107072</v>
       </c>
       <c r="E84">
-        <v>54.21200000000002</v>
+        <v>56.52800000000002</v>
       </c>
       <c r="F84">
-        <v>189.912</v>
+        <v>192.228</v>
       </c>
       <c r="G84">
         <v>2.76</v>
@@ -8169,37 +8169,37 @@
         <v>21.07</v>
       </c>
       <c r="M84">
-        <v>38.1343296</v>
+        <v>38.5993824</v>
       </c>
       <c r="N84">
-        <v>-17.0643296</v>
+        <v>-17.5293824</v>
       </c>
       <c r="O84">
-        <v>-3.754152512</v>
+        <v>-3.856464128000001</v>
       </c>
       <c r="P84">
-        <v>-13.310177088</v>
+        <v>-13.672918272</v>
       </c>
       <c r="Q84">
-        <v>-4.880177088</v>
+        <v>-5.242918272000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2451852511392777</v>
+        <v>0.256913795323941</v>
       </c>
       <c r="T84">
-        <v>4.604740211068768</v>
+        <v>4.875607282308108</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1215545165896924</v>
+        <v>0.1200900043416239</v>
       </c>
       <c r="W84">
-        <v>0.1763918530687898</v>
+        <v>0.1766859271282019</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5525205299531475</v>
+        <v>0.5458636560982904</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1903246647214776</v>
+        <v>0.1918746647214776</v>
       </c>
       <c r="C85">
-        <v>-112.3565479089293</v>
+        <v>-115.3677642435102</v>
       </c>
       <c r="D85">
-        <v>77.11145209107072</v>
+        <v>76.41623575648977</v>
       </c>
       <c r="E85">
-        <v>56.52800000000002</v>
+        <v>58.84400000000002</v>
       </c>
       <c r="F85">
-        <v>192.228</v>
+        <v>194.544</v>
       </c>
       <c r="G85">
         <v>2.76</v>
@@ -8251,37 +8251,37 @@
         <v>21.07</v>
       </c>
       <c r="M85">
-        <v>38.5993824</v>
+        <v>39.06443520000001</v>
       </c>
       <c r="N85">
-        <v>-17.5293824</v>
+        <v>-17.99443520000001</v>
       </c>
       <c r="O85">
-        <v>-3.856464128000001</v>
+        <v>-3.958775744000001</v>
       </c>
       <c r="P85">
-        <v>-13.672918272</v>
+        <v>-14.035659456</v>
       </c>
       <c r="Q85">
-        <v>-5.242918272000002</v>
+        <v>-5.605659456000005</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.256913795323941</v>
+        <v>0.2701084075316874</v>
       </c>
       <c r="T85">
-        <v>4.875607282308108</v>
+        <v>5.180332737452366</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1200900043416239</v>
+        <v>0.118660361432795</v>
       </c>
       <c r="W85">
-        <v>0.1766859271282019</v>
+        <v>0.1769729994242948</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5458636560982904</v>
+        <v>0.5393652792399772</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1918746647214776</v>
+        <v>0.1934246647214776</v>
       </c>
       <c r="C86">
-        <v>-115.3677642435102</v>
+        <v>-118.3665568164355</v>
       </c>
       <c r="D86">
-        <v>76.41623575648977</v>
+        <v>75.73344318356443</v>
       </c>
       <c r="E86">
-        <v>58.84399999999999</v>
+        <v>61.16</v>
       </c>
       <c r="F86">
-        <v>194.544</v>
+        <v>196.86</v>
       </c>
       <c r="G86">
         <v>2.76</v>
@@ -8333,37 +8333,37 @@
         <v>21.07</v>
       </c>
       <c r="M86">
-        <v>39.0644352</v>
+        <v>39.529488</v>
       </c>
       <c r="N86">
-        <v>-17.9944352</v>
+        <v>-18.459488</v>
       </c>
       <c r="O86">
-        <v>-3.958775744</v>
+        <v>-4.06108736</v>
       </c>
       <c r="P86">
-        <v>-14.035659456</v>
+        <v>-14.39840064</v>
       </c>
       <c r="Q86">
-        <v>-5.605659455999998</v>
+        <v>-5.96840064</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2701084075316872</v>
+        <v>0.2850623013671331</v>
       </c>
       <c r="T86">
-        <v>5.180332737452361</v>
+        <v>5.52568825328252</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.118660361432795</v>
+        <v>0.1172643571806445</v>
       </c>
       <c r="W86">
-        <v>0.1769729994242948</v>
+        <v>0.1772533170781266</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5393652792399773</v>
+        <v>0.5330198053665658</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1934246647214776</v>
+        <v>0.1949746647214776</v>
       </c>
       <c r="C87">
-        <v>-118.3665568164355</v>
+        <v>-121.3532557039347</v>
       </c>
       <c r="D87">
-        <v>75.73344318356443</v>
+        <v>75.0627442960653</v>
       </c>
       <c r="E87">
-        <v>61.16</v>
+        <v>63.476</v>
       </c>
       <c r="F87">
-        <v>196.86</v>
+        <v>199.176</v>
       </c>
       <c r="G87">
         <v>2.76</v>
@@ -8415,37 +8415,37 @@
         <v>21.07</v>
       </c>
       <c r="M87">
-        <v>39.529488</v>
+        <v>39.9945408</v>
       </c>
       <c r="N87">
-        <v>-18.459488</v>
+        <v>-18.9245408</v>
       </c>
       <c r="O87">
-        <v>-4.06108736</v>
+        <v>-4.163398975999999</v>
       </c>
       <c r="P87">
-        <v>-14.39840064</v>
+        <v>-14.761141824</v>
       </c>
       <c r="Q87">
-        <v>-5.96840064</v>
+        <v>-6.331141823999996</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2850623013671331</v>
+        <v>0.3021524657504998</v>
       </c>
       <c r="T87">
-        <v>5.52568825328252</v>
+        <v>5.920380271374128</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1172643571806445</v>
+        <v>0.1159008181436603</v>
       </c>
       <c r="W87">
-        <v>0.1772533170781266</v>
+        <v>0.177527115716753</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5330198053665658</v>
+        <v>0.5268219006530012</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1949746647214776</v>
+        <v>0.1965246647214776</v>
       </c>
       <c r="C88">
-        <v>-121.3532557039347</v>
+        <v>-124.3281793921973</v>
       </c>
       <c r="D88">
-        <v>75.0627442960653</v>
+        <v>74.40382060780273</v>
       </c>
       <c r="E88">
-        <v>63.476</v>
+        <v>65.792</v>
       </c>
       <c r="F88">
-        <v>199.176</v>
+        <v>201.492</v>
       </c>
       <c r="G88">
         <v>2.76</v>
@@ -8497,37 +8497,37 @@
         <v>21.07</v>
       </c>
       <c r="M88">
-        <v>39.9945408</v>
+        <v>40.4595936</v>
       </c>
       <c r="N88">
-        <v>-18.9245408</v>
+        <v>-19.3895936</v>
       </c>
       <c r="O88">
-        <v>-4.163398975999999</v>
+        <v>-4.265710592</v>
       </c>
       <c r="P88">
-        <v>-14.761141824</v>
+        <v>-15.123883008</v>
       </c>
       <c r="Q88">
-        <v>-6.331141823999996</v>
+        <v>-6.693883007999998</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3021524657504998</v>
+        <v>0.3218718861928458</v>
       </c>
       <c r="T88">
-        <v>5.920380271374128</v>
+        <v>6.375794138402907</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1159008181436603</v>
+        <v>0.1145686248316642</v>
       </c>
       <c r="W88">
-        <v>0.177527115716753</v>
+        <v>0.1777946201338018</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5268219006530012</v>
+        <v>0.5207664765075644</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1965246647214776</v>
+        <v>0.1980746647214776</v>
       </c>
       <c r="C89">
-        <v>-124.3281793921973</v>
+        <v>-127.291635281651</v>
       </c>
       <c r="D89">
-        <v>74.40382060780273</v>
+        <v>73.75636471834895</v>
       </c>
       <c r="E89">
-        <v>65.792</v>
+        <v>68.108</v>
       </c>
       <c r="F89">
-        <v>201.492</v>
+        <v>203.808</v>
       </c>
       <c r="G89">
         <v>2.76</v>
@@ -8579,37 +8579,37 @@
         <v>21.07</v>
       </c>
       <c r="M89">
-        <v>40.4595936</v>
+        <v>40.9246464</v>
       </c>
       <c r="N89">
-        <v>-19.3895936</v>
+        <v>-19.8546464</v>
       </c>
       <c r="O89">
-        <v>-4.265710592</v>
+        <v>-4.368022208</v>
       </c>
       <c r="P89">
-        <v>-15.123883008</v>
+        <v>-15.486624192</v>
       </c>
       <c r="Q89">
-        <v>-6.693883007999998</v>
+        <v>-7.056624192000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3218718861928458</v>
+        <v>0.3448778767089164</v>
       </c>
       <c r="T89">
-        <v>6.375794138402907</v>
+        <v>6.90711031660315</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1145686248316642</v>
+        <v>0.1132667086403952</v>
       </c>
       <c r="W89">
-        <v>0.1777946201338018</v>
+        <v>0.1780560449050086</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5207664765075644</v>
+        <v>0.5148486756381602</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1980746647214776</v>
+        <v>0.1996246647214776</v>
       </c>
       <c r="C90">
-        <v>-127.291635281651</v>
+        <v>-130.243920165138</v>
       </c>
       <c r="D90">
-        <v>73.75636471834895</v>
+        <v>73.12007983486204</v>
       </c>
       <c r="E90">
-        <v>68.108</v>
+        <v>70.42400000000001</v>
       </c>
       <c r="F90">
-        <v>203.808</v>
+        <v>206.124</v>
       </c>
       <c r="G90">
         <v>2.76</v>
@@ -8661,37 +8661,37 @@
         <v>21.07</v>
       </c>
       <c r="M90">
-        <v>40.9246464</v>
+        <v>41.3896992</v>
       </c>
       <c r="N90">
-        <v>-19.8546464</v>
+        <v>-20.3196992</v>
       </c>
       <c r="O90">
-        <v>-4.368022208</v>
+        <v>-4.470333824000001</v>
       </c>
       <c r="P90">
-        <v>-15.486624192</v>
+        <v>-15.849365376</v>
       </c>
       <c r="Q90">
-        <v>-7.056624192000001</v>
+        <v>-7.419365376000002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3448778767089164</v>
+        <v>0.3720667745915451</v>
       </c>
       <c r="T90">
-        <v>6.90711031660315</v>
+        <v>7.535029436294345</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1132667086403952</v>
+        <v>0.1119940489927504</v>
       </c>
       <c r="W90">
-        <v>0.1780560449050086</v>
+        <v>0.1783115949622557</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5148486756381602</v>
+        <v>0.5090638590579561</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1996246647214776</v>
+        <v>0.2011746647214776</v>
       </c>
       <c r="C91">
-        <v>-130.243920165138</v>
+        <v>-133.1853206815504</v>
       </c>
       <c r="D91">
-        <v>73.12007983486204</v>
+        <v>72.49467931844963</v>
       </c>
       <c r="E91">
-        <v>70.42400000000001</v>
+        <v>72.74000000000001</v>
       </c>
       <c r="F91">
-        <v>206.124</v>
+        <v>208.44</v>
       </c>
       <c r="G91">
         <v>2.76</v>
@@ -8743,37 +8743,37 @@
         <v>21.07</v>
       </c>
       <c r="M91">
-        <v>41.3896992</v>
+        <v>41.854752</v>
       </c>
       <c r="N91">
-        <v>-20.3196992</v>
+        <v>-20.784752</v>
       </c>
       <c r="O91">
-        <v>-4.470333824000001</v>
+        <v>-4.57264544</v>
       </c>
       <c r="P91">
-        <v>-15.849365376</v>
+        <v>-16.21210656</v>
       </c>
       <c r="Q91">
-        <v>-7.419365376000002</v>
+        <v>-7.782106559999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3720667745915451</v>
+        <v>0.4046934520506997</v>
       </c>
       <c r="T91">
-        <v>7.535029436294345</v>
+        <v>8.288532379923781</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1119940489927504</v>
+        <v>0.1107496706706087</v>
       </c>
       <c r="W91">
-        <v>0.1783115949622557</v>
+        <v>0.1785614661293418</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5090638590579561</v>
+        <v>0.5034075939573122</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2011746647214776</v>
+        <v>0.2351644246740361</v>
       </c>
       <c r="C92">
-        <v>-133.1853206815504</v>
+        <v>-146.9508835127316</v>
       </c>
       <c r="D92">
-        <v>72.49467931844963</v>
+        <v>61.04511648726841</v>
       </c>
       <c r="E92">
-        <v>72.74000000000001</v>
+        <v>75.05600000000001</v>
       </c>
       <c r="F92">
-        <v>208.44</v>
+        <v>210.756</v>
       </c>
       <c r="G92">
         <v>2.76</v>
@@ -8825,45 +8825,45 @@
         <v>21.07</v>
       </c>
       <c r="M92">
-        <v>41.854752</v>
+        <v>49.6962648</v>
       </c>
       <c r="N92">
-        <v>-20.784752</v>
+        <v>-28.6262648</v>
       </c>
       <c r="O92">
-        <v>-4.57264544</v>
+        <v>-6.297778256</v>
       </c>
       <c r="P92">
-        <v>-16.21210656</v>
+        <v>-22.328486544</v>
       </c>
       <c r="Q92">
-        <v>-7.782106559999999</v>
+        <v>-13.898486544</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4046934520506997</v>
+        <v>0.4511233906403168</v>
       </c>
       <c r="T92">
-        <v>8.288532379923781</v>
+        <v>9.360817335804084</v>
       </c>
       <c r="U92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1107496706706087</v>
+        <v>0.09327461568097568</v>
       </c>
       <c r="W92">
-        <v>0.1785614661293418</v>
+        <v>0.2138058456224259</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.5034075939573122</v>
+        <v>0.4239755258226168</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2351644246740361</v>
+        <v>0.2370644246740361</v>
       </c>
       <c r="C93">
-        <v>-146.9508835127316</v>
+        <v>-149.8011056091034</v>
       </c>
       <c r="D93">
-        <v>61.04511648726841</v>
+        <v>60.5108943908966</v>
       </c>
       <c r="E93">
-        <v>75.05600000000001</v>
+        <v>77.37200000000001</v>
       </c>
       <c r="F93">
-        <v>210.756</v>
+        <v>213.072</v>
       </c>
       <c r="G93">
         <v>2.76</v>
@@ -8907,37 +8907,37 @@
         <v>21.07</v>
       </c>
       <c r="M93">
-        <v>49.6962648</v>
+        <v>50.2423776</v>
       </c>
       <c r="N93">
-        <v>-28.6262648</v>
+        <v>-29.1723776</v>
       </c>
       <c r="O93">
-        <v>-6.297778256</v>
+        <v>-6.417923072000001</v>
       </c>
       <c r="P93">
-        <v>-22.328486544</v>
+        <v>-22.754454528</v>
       </c>
       <c r="Q93">
-        <v>-13.898486544</v>
+        <v>-14.324454528</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4511233906403168</v>
+        <v>0.5017888144703565</v>
       </c>
       <c r="T93">
-        <v>9.360817335804084</v>
+        <v>10.5309195027796</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09327461568097568</v>
+        <v>0.09226076116270419</v>
       </c>
       <c r="W93">
-        <v>0.2138058456224259</v>
+        <v>0.2140449125178344</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4239755258226168</v>
+        <v>0.4193670961941101</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2370644246740361</v>
+        <v>0.2389644246740361</v>
       </c>
       <c r="C94">
-        <v>-149.8011056091034</v>
+        <v>-152.6420585819407</v>
       </c>
       <c r="D94">
-        <v>60.5108943908966</v>
+        <v>59.98594141805928</v>
       </c>
       <c r="E94">
-        <v>77.37200000000001</v>
+        <v>79.68800000000002</v>
       </c>
       <c r="F94">
-        <v>213.072</v>
+        <v>215.388</v>
       </c>
       <c r="G94">
         <v>2.76</v>
@@ -8989,37 +8989,37 @@
         <v>21.07</v>
       </c>
       <c r="M94">
-        <v>50.2423776</v>
+        <v>50.7884904</v>
       </c>
       <c r="N94">
-        <v>-29.1723776</v>
+        <v>-29.7184904</v>
       </c>
       <c r="O94">
-        <v>-6.417923072000001</v>
+        <v>-6.538067888</v>
       </c>
       <c r="P94">
-        <v>-22.754454528</v>
+        <v>-23.180422512</v>
       </c>
       <c r="Q94">
-        <v>-14.324454528</v>
+        <v>-14.750422512</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5017888144703565</v>
+        <v>0.5669300736804075</v>
       </c>
       <c r="T94">
-        <v>10.5309195027796</v>
+        <v>12.03533657460525</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09226076116270419</v>
+        <v>0.09126870996740631</v>
       </c>
       <c r="W94">
-        <v>0.2140449125178344</v>
+        <v>0.2142788381896856</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4193670961941101</v>
+        <v>0.4148577725791196</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2389644246740361</v>
+        <v>0.2408644246740361</v>
       </c>
       <c r="C95">
-        <v>-152.6420585819407</v>
+        <v>-155.4739815949891</v>
       </c>
       <c r="D95">
-        <v>59.98594141805928</v>
+        <v>59.47001840501093</v>
       </c>
       <c r="E95">
-        <v>79.68800000000002</v>
+        <v>82.00400000000002</v>
       </c>
       <c r="F95">
-        <v>215.388</v>
+        <v>217.704</v>
       </c>
       <c r="G95">
         <v>2.76</v>
@@ -9071,37 +9071,37 @@
         <v>21.07</v>
       </c>
       <c r="M95">
-        <v>50.7884904</v>
+        <v>51.3346032</v>
       </c>
       <c r="N95">
-        <v>-29.7184904</v>
+        <v>-30.2646032</v>
       </c>
       <c r="O95">
-        <v>-6.538067888</v>
+        <v>-6.658212704000001</v>
       </c>
       <c r="P95">
-        <v>-23.180422512</v>
+        <v>-23.606390496</v>
       </c>
       <c r="Q95">
-        <v>-14.750422512</v>
+        <v>-15.176390496</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5669300736804075</v>
+        <v>0.6537850859604755</v>
       </c>
       <c r="T95">
-        <v>12.03533657460525</v>
+        <v>14.04122600370613</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09126870996740631</v>
+        <v>0.09029776624434879</v>
       </c>
       <c r="W95">
-        <v>0.2142788381896856</v>
+        <v>0.2145077867195826</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4148577725791196</v>
+        <v>0.4104443920197672</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2408644246740361</v>
+        <v>0.2427644246740361</v>
       </c>
       <c r="C96">
-        <v>-155.4739815949891</v>
+        <v>-158.2971056542235</v>
       </c>
       <c r="D96">
-        <v>59.47001840501093</v>
+        <v>58.96289434577653</v>
       </c>
       <c r="E96">
-        <v>82.00400000000002</v>
+        <v>84.32000000000002</v>
       </c>
       <c r="F96">
-        <v>217.704</v>
+        <v>220.02</v>
       </c>
       <c r="G96">
         <v>2.76</v>
@@ -9153,37 +9153,37 @@
         <v>21.07</v>
       </c>
       <c r="M96">
-        <v>51.3346032</v>
+        <v>51.88071600000001</v>
       </c>
       <c r="N96">
-        <v>-30.2646032</v>
+        <v>-30.81071600000001</v>
       </c>
       <c r="O96">
-        <v>-6.658212704000001</v>
+        <v>-6.778357520000001</v>
       </c>
       <c r="P96">
-        <v>-23.606390496</v>
+        <v>-24.03235848000001</v>
       </c>
       <c r="Q96">
-        <v>-15.176390496</v>
+        <v>-15.60235848000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6537850859604755</v>
+        <v>0.7753821031525709</v>
       </c>
       <c r="T96">
-        <v>14.04122600370613</v>
+        <v>16.84947120444737</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09029776624434879</v>
+        <v>0.08934726344177669</v>
       </c>
       <c r="W96">
-        <v>0.2145077867195826</v>
+        <v>0.2147319152804291</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4104443920197672</v>
+        <v>0.4061239247353486</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2427644246740361</v>
+        <v>0.2446644246740362</v>
       </c>
       <c r="C97">
-        <v>-158.2971056542235</v>
+        <v>-161.1116539527301</v>
       </c>
       <c r="D97">
-        <v>58.96289434577653</v>
+        <v>58.46434604726986</v>
       </c>
       <c r="E97">
-        <v>84.32000000000002</v>
+        <v>86.63600000000002</v>
       </c>
       <c r="F97">
-        <v>220.02</v>
+        <v>222.336</v>
       </c>
       <c r="G97">
         <v>2.76</v>
@@ -9235,37 +9235,37 @@
         <v>21.07</v>
       </c>
       <c r="M97">
-        <v>51.88071600000001</v>
+        <v>52.4268288</v>
       </c>
       <c r="N97">
-        <v>-30.81071600000001</v>
+        <v>-31.3568288</v>
       </c>
       <c r="O97">
-        <v>-6.778357520000001</v>
+        <v>-6.898502336000001</v>
       </c>
       <c r="P97">
-        <v>-24.03235848000001</v>
+        <v>-24.458326464</v>
       </c>
       <c r="Q97">
-        <v>-15.60235848000001</v>
+        <v>-16.028326464</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7753821031525709</v>
+        <v>0.9577776289407142</v>
       </c>
       <c r="T97">
-        <v>16.84947120444737</v>
+        <v>21.06183900555922</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.08934726344177669</v>
+        <v>0.08841656278092486</v>
       </c>
       <c r="W97">
-        <v>0.2147319152804291</v>
+        <v>0.214951374496258</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4061239247353486</v>
+        <v>0.4018934671860221</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2446644246740361</v>
+        <v>0.2465644246740361</v>
       </c>
       <c r="C98">
-        <v>-161.1116539527301</v>
+        <v>-163.917842198238</v>
       </c>
       <c r="D98">
-        <v>58.46434604726988</v>
+        <v>57.97415780176197</v>
       </c>
       <c r="E98">
-        <v>86.636</v>
+        <v>88.952</v>
       </c>
       <c r="F98">
-        <v>222.336</v>
+        <v>224.652</v>
       </c>
       <c r="G98">
         <v>2.76</v>
@@ -9317,37 +9317,37 @@
         <v>21.07</v>
       </c>
       <c r="M98">
-        <v>52.4268288</v>
+        <v>52.9729416</v>
       </c>
       <c r="N98">
-        <v>-31.3568288</v>
+        <v>-31.9029416</v>
       </c>
       <c r="O98">
-        <v>-6.898502335999999</v>
+        <v>-7.018647152</v>
       </c>
       <c r="P98">
-        <v>-24.458326464</v>
+        <v>-24.884294448</v>
       </c>
       <c r="Q98">
-        <v>-16.028326464</v>
+        <v>-16.454294448</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9577776289407116</v>
+        <v>1.261770171920949</v>
       </c>
       <c r="T98">
-        <v>21.06183900555916</v>
+        <v>28.08245200741222</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.08841656278092487</v>
+        <v>0.08750505182442049</v>
       </c>
       <c r="W98">
-        <v>0.2149513744962579</v>
+        <v>0.2151663087798017</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4018934671860221</v>
+        <v>0.3977502355655477</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2465644246740361</v>
+        <v>0.2484644246740361</v>
       </c>
       <c r="C99">
-        <v>-163.917842198238</v>
+        <v>-166.7158789243109</v>
       </c>
       <c r="D99">
-        <v>57.97415780176197</v>
+        <v>57.49212107568906</v>
       </c>
       <c r="E99">
-        <v>88.952</v>
+        <v>91.268</v>
       </c>
       <c r="F99">
-        <v>224.652</v>
+        <v>226.968</v>
       </c>
       <c r="G99">
         <v>2.76</v>
@@ -9399,37 +9399,37 @@
         <v>21.07</v>
       </c>
       <c r="M99">
-        <v>52.9729416</v>
+        <v>53.5190544</v>
       </c>
       <c r="N99">
-        <v>-31.9029416</v>
+        <v>-32.4490544</v>
       </c>
       <c r="O99">
-        <v>-7.018647152</v>
+        <v>-7.138791968</v>
       </c>
       <c r="P99">
-        <v>-24.884294448</v>
+        <v>-25.310262432</v>
       </c>
       <c r="Q99">
-        <v>-16.454294448</v>
+        <v>-16.880262432</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.261770171920949</v>
+        <v>1.869755257881424</v>
       </c>
       <c r="T99">
-        <v>28.08245200741222</v>
+        <v>42.12367801111833</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.08750505182442049</v>
+        <v>0.08661214313233458</v>
       </c>
       <c r="W99">
-        <v>0.2151663087798017</v>
+        <v>0.2153768566493955</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3977502355655477</v>
+        <v>0.3936915596924299</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2484644246740361</v>
+        <v>0.2503644246740361</v>
       </c>
       <c r="C100">
-        <v>-166.7158789243109</v>
+        <v>-169.5059657861424</v>
       </c>
       <c r="D100">
-        <v>57.49212107568906</v>
+        <v>57.01803421385755</v>
       </c>
       <c r="E100">
-        <v>91.268</v>
+        <v>93.584</v>
       </c>
       <c r="F100">
-        <v>226.968</v>
+        <v>229.284</v>
       </c>
       <c r="G100">
         <v>2.76</v>
@@ -9481,37 +9481,37 @@
         <v>21.07</v>
       </c>
       <c r="M100">
-        <v>53.5190544</v>
+        <v>54.0651672</v>
       </c>
       <c r="N100">
-        <v>-32.4490544</v>
+        <v>-32.9951672</v>
       </c>
       <c r="O100">
-        <v>-7.138791968</v>
+        <v>-7.258936783999999</v>
       </c>
       <c r="P100">
-        <v>-25.310262432</v>
+        <v>-25.736230416</v>
       </c>
       <c r="Q100">
-        <v>-16.880262432</v>
+        <v>-17.306230416</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.869755257881424</v>
+        <v>3.693710515762847</v>
       </c>
       <c r="T100">
-        <v>42.12367801111833</v>
+        <v>84.24735602223666</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.08661214313233458</v>
+        <v>0.08573727299968473</v>
       </c>
       <c r="W100">
-        <v>0.2153768566493955</v>
+        <v>0.2155831510266744</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3936915596924299</v>
+        <v>0.3897148772712942</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2503644246740361</v>
-      </c>
-      <c r="C101">
-        <v>-169.5059657861424</v>
-      </c>
-      <c r="D101">
-        <v>57.01803421385755</v>
-      </c>
-      <c r="E101">
-        <v>93.584</v>
-      </c>
-      <c r="F101">
-        <v>229.284</v>
-      </c>
-      <c r="G101">
-        <v>2.76</v>
-      </c>
-      <c r="H101">
-        <v>95.90000000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>29.5</v>
-      </c>
-      <c r="K101">
-        <v>8.43</v>
-      </c>
-      <c r="L101">
-        <v>21.07</v>
-      </c>
-      <c r="M101">
-        <v>54.0651672</v>
-      </c>
-      <c r="N101">
-        <v>-32.9951672</v>
-      </c>
-      <c r="O101">
-        <v>-7.258936783999999</v>
-      </c>
-      <c r="P101">
-        <v>-25.736230416</v>
-      </c>
-      <c r="Q101">
-        <v>-17.306230416</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.693710515762847</v>
-      </c>
-      <c r="T101">
-        <v>84.24735602223666</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.08573727299968473</v>
-      </c>
-      <c r="W101">
-        <v>0.2155831510266744</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3897148772712942</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
